--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,77 +555,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/fc-andorra-vs-real-sociedad-ii/1635855508</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/kups-vs-hjk-helsinki/1635941147</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 12:00</t>
+          <t>2026-09-13 12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.710</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,67 +668,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-fc-haka/1635888173</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sporting-gijon-vs-eldense/1635984801</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-12 12:00</t>
+          <t>2026-09-13 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.420</t>
+          <t>1.662</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.080</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>5.520</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -738,37 +738,37 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,62 +781,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-korona-kielce/1635812816</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/arges-pitesti-vs-botosani/1635984802</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12 12:45</t>
+          <t>2026-09-13 12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.830</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -856,32 +856,32 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,77 +894,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-sjk-akatemia/1635886111</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-miedz-legnica/1635984819</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00</t>
+          <t>2026-09-13 12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,27 +974,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,67 +1007,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-hjk-klubi-04/1635893219</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-wieczysta-krakow/1635941158</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00</t>
+          <t>2026-09-13 12:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>1.892</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,62 +1120,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/ruch-chorzow-vs-podbeskidzie-bielsko-biala/1635119276</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-oddevold/1635992329</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30</t>
+          <t>2026-09-13 13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Podbeskidzie Bielsko-Biala</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.434</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>5.140</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>6.220</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1185,42 +1185,42 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,107 +1233,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-siedlce/1635113923</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-real-oviedo/1635995401</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30</t>
+          <t>2026-09-13 14:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.150</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,47 +1346,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-tps/1635793996</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-falkenbergs/1635995317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-12 09:53</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1396,57 +1396,57 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cadiz-vs-las-palmas/1635910217</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-asane/1635941038</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-12 14:15</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>4.830</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>4.530</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,107 +1572,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gornik-zabrze-vs-lech-poznan/1635809687</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-sandnes-ulf/1635932695</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.010</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>6.310</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>8.190</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,107 +1685,107 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/sepsi-vs-cfr-cluj/1635909134</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-strommen/1635992406</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>4.560</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,107 +1798,107 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-fc-lahti/1635812819</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-odd-bk/1635941034</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-12 09:53</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>5.960</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>5.200</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.890</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,102 +1911,102 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-gnistan/1635790307</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-kongsvinger/1635932688</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-12 09:53</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.370</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.620</t>
+          <t>4.520</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.990</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2024,107 +2024,107 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-albacete/1635920602</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/moss-vs-haugesund/1635941046</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-12 16:30</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>4.990</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>5.170</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.100</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,102 +2137,102 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-castellon/1635920601</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-lyn/1635932683</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-12 16:30</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>4.110</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>2.640</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.980</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2250,107 +2250,107 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-stabaek/1635793998</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-stal-rzeszow/1635992400</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-12 18:00</t>
+          <t>2026-09-13 15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2363,12 +2363,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/zaglebie-lubin-vs-gks-katowice/1635918972</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-widzew-lodz/1635941041</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-12 18:15</t>
+          <t>2026-09-13 15:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2378,47 +2378,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.670</t>
+          <t>4.350</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2428,42 +2428,42 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2476,107 +2476,107 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-voluntari/1635919063</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-umf-njardvik/1635995448</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-12 18:30</t>
+          <t>2026-09-13 16:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rapid Bucuresti</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.684</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.970</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.030</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>1.869</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1.781</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2589,12 +2589,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cordoba-vs-almeria/1635920660</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-sabadell/1636004865</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-12 19:00</t>
+          <t>2026-09-13 16:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2604,57 +2604,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.840</t>
+          <t>4.430</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2664,32 +2664,32 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2702,85 +2702,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-pogon-grodzisk-mazowiecki/1635984761</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/corvinul-hunedoara-vs-universitatea-craiova/1636007200</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-13 10:00</t>
+          <t>2026-09-13 17:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2791,107 +2815,107 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-plock-vs-cracovia-krakow/1635941152</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-leganes/1636007501</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-13 10:15</t>
+          <t>2026-09-13 19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2904,32 +2928,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/kups-vs-hjk-helsinki/1635941147</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-criciuma/1636007503</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00</t>
+          <t>2026-09-13 19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2939,12 +2963,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>3.920</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2954,42 +2978,42 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2999,12 +3023,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3017,47 +3041,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sporting-gijon-vs-eldense/1635984801</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1635995399</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00</t>
+          <t>2026-09-13 19:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>4.350</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.090</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3067,57 +3091,57 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3130,107 +3154,107 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/arges-pitesti-vs-botosani/1635984802</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-athletic-club/1636019331</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00</t>
+          <t>2026-09-13 21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.709</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.900</t>
+          <t>5.760</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>1.775</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>1.877</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3243,85 +3267,109 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-miedz-legnica/1635984819</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ceara/1636007562</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-13 12:30</t>
+          <t>2026-09-13 21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>4.470</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3332,85 +3380,109 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-wieczysta-krakow/1635941158</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-cuiaba/1636020865</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-13 12:45</t>
+          <t>2026-09-13 21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>5.660</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3421,92 +3493,92 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-oddevold/1635992329</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/inter-turku-vs-vps/1636039434</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-13 13:00</t>
+          <t>2026-09-14 15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.950</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5.840</t>
+          <t>4.930</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3516,12 +3588,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -3534,107 +3606,107 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-real-oviedo/1635995401</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-cluj-vs-otelul-galati/1636040079</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-13 14:15</t>
+          <t>2026-09-14 15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>1.684</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.940</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>4.560</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>1.869</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1.980</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3647,12 +3719,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-falkenbergs/1635995317</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/orebro-sk-vs-nordic-united/1636048869</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3662,47 +3734,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>2.890</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3712,12 +3784,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3727,27 +3799,27 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -3760,85 +3832,109 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-asane/1635941038</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrby-vs-varbergs-bois/1636040112</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.568</t>
+          <t>2.840</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.790</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3849,62 +3945,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-kongsvinger/1635932688</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-piast-gliwice/1636048868</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3914,42 +4010,42 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -3962,109 +4058,85 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-odd-bk/1635941034</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-nieciecza/1636021027</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5.180</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.850</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.490</t>
+          <t>2.640</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -4075,107 +4147,107 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/moss-vs-haugesund/1635941046</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ostersunds-fk-vs-helsingborgs/1636048880</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 17:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.860</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.930</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4188,107 +4260,107 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-lyn/1635932683</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/fcsb-vs-petrolul-ploiesti/1636048892</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 18:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Petrolul Ploiesti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.410</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>4.600</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>6.810</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -4301,107 +4373,107 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-strommen/1635992406</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-eibar/1636031170</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 18:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.350</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -4414,107 +4486,107 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-stal-rzeszow/1635992400</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-goias/1636054659</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-13 15:00</t>
+          <t>2026-09-14 22:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stal Rzeszow</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>2.310</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2.950</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3.520</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.620</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3.650</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4527,107 +4599,107 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-widzew-lodz/1635941041</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/avai-vs-vila-nova/1636054675</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-13 15:30</t>
+          <t>2026-09-15 00:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -4640,32 +4712,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-umf-njardvik/1635995448</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-zaglebie-lubin/1636090422</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-13 16:15</t>
+          <t>2026-09-15 16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4675,12 +4747,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4690,22 +4762,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4715,22 +4787,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4753,107 +4825,107 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-sabadell/1636004865</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-sundsvall/1636090438</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-13 16:30</t>
+          <t>2026-09-15 17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5.110</t>
+          <t>6.250</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -4866,57 +4938,57 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/corvinul-hunedoara-vs-universitatea-craiova/1636007200</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-sandvikens-if/1636090545</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-13 17:30</t>
+          <t>2026-09-15 17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>2.610</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4924,27 +4996,51 @@
           <t>1.854</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -4955,107 +5051,107 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-leganes/1636007501</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varnamo-vs-osters/1636115615</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00</t>
+          <t>2026-09-15 17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.610</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -5068,107 +5164,107 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-criciuma/1636007503</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/korona-kielce-vs-gornik-zabrze/1636120194</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00</t>
+          <t>2026-09-15 18:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -5181,12 +5277,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-athletic-club/1636019331</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-operario-ferroviario/1636120243</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-13 21:00</t>
+          <t>2026-09-15 22:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5196,77 +5292,77 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5.590</t>
+          <t>4.130</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5276,12 +5372,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -5294,12 +5390,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ceara/1636007562</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-ponte-preta/1636119643</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-13 21:30</t>
+          <t>2026-09-15 22:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5309,92 +5405,92 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.284</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>5.540</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4.680</t>
+          <t>9.630</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>1.806</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -5407,12 +5503,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-cuiaba/1636020865</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-sport-recife/1636131222</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-13 21:30</t>
+          <t>2026-09-16 00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5422,47 +5518,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.520</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5472,42 +5568,42 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -5520,12 +5616,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/inter-turku-vs-vps/1636039434</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5535,94 +5631,70 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.520</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4.920</t>
+          <t>5.650</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
@@ -5633,47 +5705,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-cluj-vs-otelul-galati/1636040079</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14 15:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4.560</t>
+          <t>4.440</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5683,59 +5755,35 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -5746,109 +5794,85 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/orebro-sk-vs-nordic-united/1636048869</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/uta-arad-vs-sepsi/1636346520</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>4.110</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -5859,109 +5883,85 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrby-vs-varbergs-bois/1636040112</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00</t>
+          <t>2026-09-18 15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.840</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>4.610</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>5.430</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -5972,79 +5972,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-piast-gliwice/1636048868</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00</t>
+          <t>2026-09-18 15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-12 09:56</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.380</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -6052,29 +6040,17 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
@@ -6085,12 +6061,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-nieciecza/1636021027</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00</t>
+          <t>2026-09-18 16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6100,47 +6076,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -6153,12 +6129,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
@@ -6174,109 +6150,85 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ostersunds-fk-vs-helsingborgs/1636048880</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-14 17:05</t>
+          <t>2026-09-18 18:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -6287,109 +6239,85 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/fcsb-vs-petrolul-ploiesti/1636048892</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-14 18:00</t>
+          <t>2026-09-18 18:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-12 09:57</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.580</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6.300</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -6400,62 +6328,62 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-eibar/1636031170</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30</t>
+          <t>2026-09-18 18:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2.880</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -6463,17 +6391,17 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
@@ -6489,109 +6417,85 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-sao-bernardo/1636059037</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-14 22:30</t>
+          <t>2026-09-19 12:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:53</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
@@ -6602,109 +6506,85 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-goias/1636054659</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-lks-lodz/1635909034</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-14 22:30</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2.930</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -6715,109 +6595,85 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/avai-vs-vila-nova/1636054675</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-15 00:30</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-12 09:55</t>
+          <t>2026-09-13 10:56</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -6828,109 +6684,85 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-sundsvall/1636090438</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-ktp/1636463842</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5.330</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
@@ -6941,79 +6773,67 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varnamo-vs-osters/1636115615</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00</t>
+          <t>2026-09-19 15:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:54</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>3</t>
@@ -7021,29 +6841,17 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
@@ -7054,109 +6862,85 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-sandvikens-if/1636090545</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-12 09:54</t>
+          <t>2026-09-13 10:55</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.610</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -7164,208 +6948,6 @@
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-operario-ferroviario/1636120243</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-15 22:30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Operario Ferroviario</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-09-12 09:55</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>3.410</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4.130</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-sport-recife/1636131222</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-16 00:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-09-12 09:56</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>3.460</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>4.460</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -552,6 +552,6161 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-zaglebie-lubin/1636090422</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Zaglebie Lubin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.700</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.230</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-sundsvall/1636090438</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.390</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.030</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7.430</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varnamo-vs-osters/1636115615</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Varnamo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Osters</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.720</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-sandvikens-if/1636090545</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Brage</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sandvikens IF</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.970</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.730</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.250</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/korona-kielce-vs-gornik-zabrze/1636120194</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Korona Kielce</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.780</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.270</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2.680</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-ponte-preta/1636119643</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.344</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5.390</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8.680</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-operario-ferroviario/1636120243</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nautico</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Operario Ferroviario</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.390</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4.370</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-sport-recife/1636131222</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.460</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3.780</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.751</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.930</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.400</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FC Lahti</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.526</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.460</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5.640</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/uta-arad-vs-sepsi/1636346520</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sepsi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.630</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4.110</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JaPS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EIF</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.650</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3.480</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.490</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FC Haka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HJK Klubi 04</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.476</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.670</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5.440</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HJK Helsinki</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3.770</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4.010</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-inter-turku/1636378694</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AC Oulu</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Inter Turku</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4.220</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.610</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/widzew-lodz-vs-wieczysta-krakow/1636378696</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Widzew Lodz</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Wieczysta Krakow</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4.040</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Warta Poznan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Puszcza Niepolomice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.650</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.140</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/falkenbergs-vs-ostersunds-fk/1636382438</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Falkenbergs</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ostersunds FK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2.370</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3.240</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3.030</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-arges-pitesti/1636378753</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rapid Bucuresti</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Arges Pitesti</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.729</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.480</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4.960</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2.440</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.530</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.810</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wisla Krakow</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Slask Wroclaw</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.636</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4.230</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4.680</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:45</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Polonia Bytom</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2.760</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.460</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2.410</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.507</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4.050</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6.580</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Atletico Goianiense</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2.360</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.190</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3.140</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-19 10:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Stal Mielec</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3.240</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2.590</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.670</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2.550</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-sociedad-ii-vs-mallorca/1636442645</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3.930</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3.600</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-jippo/1636581425</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mikkelin Palloilijat</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JIPPO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>4.490</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.910</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.684</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Polonia Warsaw</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3.690</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4.070</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-lks-lodz/1635909034</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pogon Grodzisk Mazowiecki</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LKS Lodz</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3.310</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3.440</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Nieciecza</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Odra Opole</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3.690</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3.560</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-kups/1636463837</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3.180</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.470</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2.240</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-vs-bryne/1636463898</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Asane</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3.390</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.880</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-ktp/1636463842</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PK-35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>KTP</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3.620</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2.190</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/fc-andorra-vs-sporting-gijon/1636463851</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:15</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sporting Gijon</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3.530</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3.580</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/cfr-cluj-vs-botosani/1636480675</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Botosani</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.730</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3.390</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-19 15:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SJK Akatemia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>KaPa</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2.360</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3.770</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2.650</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-19 15:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GKS Katowice</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cracovia Krakow</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.340</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.610</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2.850</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.920</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.100</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.600</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.561</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4.250</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5.530</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/miedz-legnica-vs-stal-rzeszow/1635909114</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Miedz Legnica</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Stal Rzeszow</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.609</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4.210</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4.670</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-craiova-vs-fcsb/1636486507</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3.800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4.150</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cadiz-vs-girona/1636486543</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3.790</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.480</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-botafogo-sp/1636506150</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-19 21:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.370</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2.920</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3.440</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-pogon-szczecin/1636498184</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Piast Gliwice</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2.470</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.530</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2.720</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/voluntari-vs-universitatea-cluj/1636537327</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Voluntari</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Universitatea Cluj</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3.200</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3.560</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2.130</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sabadell-vs-real-oviedo/1636554000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sabadell</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2.430</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2.990</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3.300</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-siedlce-vs-arka-gdynia/1635909115</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pogon Siedlce</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>4.210</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.660</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/helsingborgs-vs-norrby/1636554051</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Helsingborgs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Norrby</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>3.740</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3.180</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-valladolid/1636569764</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:15</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ceuta</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Real Valladolid</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2.900</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3.350</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2.460</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2.180</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>3.770</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2.970</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Stromsgodset</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7.930</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6.090</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1.271</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>+1.75</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ranheim</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.729</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4.510</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3.740</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Strommen</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.259</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6.380</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8.000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.404</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>5.330</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5.850</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Hodd</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.276</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>5.530</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>9.000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Odd BK</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Egersunds</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1.714</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>4.310</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3.940</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-legia-warsaw/1636498762</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Legia Warsaw</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2.920</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3.430</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2.370</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-unia-skierniewice/1635909033</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Podbeskidzie Bielsko-Biala</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Unia Skierniewice</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3.680</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3.210</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-20 16:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Celta Vigo II</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.387</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4.940</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>7.430</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-20 16:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2.940</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4.400</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/dinamo-bucuresti-vs-farul-constanta/1636572912</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Dinamo Bucuresti</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.628</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>3.900</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5.030</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/lech-poznan-vs-radomiak-radom/1636498768</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:15</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.266</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6.070</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8.680</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-granada/1636572929</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3.190</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4.120</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-avai/1636578432</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4.590</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/otelul-galati-vs-corvinul-hunedoara/1636611974</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Otelul Galati</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Corvinul Hunedoara</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2.420</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>3.130</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3.070</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-21 18:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Petrolul Ploiesti</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Csikszereda</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.699</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3.650</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4.850</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,109 +555,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-zaglebie-lubin/1636090422</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 16:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:36</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.890</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.360</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3.700</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4.230</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -668,79 +644,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-sundsvall/1636090438</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:36</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.390</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.030</t>
+          <t>4.380</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.430</t>
+          <t>5.430</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
           <t>1.909</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -748,29 +712,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -781,109 +733,85 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varnamo-vs-osters/1636115615</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/uta-arad-vs-sepsi/1636346520</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00</t>
+          <t>2026-09-18 15:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -894,109 +822,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-sandvikens-if/1636090545</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00</t>
+          <t>2026-09-18 15:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1007,109 +911,85 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/korona-kielce-vs-gornik-zabrze/1636120194</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 18:30</t>
+          <t>2026-09-18 15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>1.456</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>4.800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>5.560</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1120,109 +1000,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-ponte-preta/1636119643</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:30</t>
+          <t>2026-09-18 16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.390</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8.680</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1233,79 +1089,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-operario-ferroviario/1636120243</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-inter-turku/1636378694</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:30</t>
+          <t>2026-09-18 16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:36</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1313,29 +1157,17 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1346,47 +1178,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-sport-recife/1636131222</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/widzew-lodz-vs-wieczysta-krakow/1636378696</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-16 00:00</t>
+          <t>2026-09-18 16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1396,59 +1228,35 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1459,62 +1267,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00</t>
+          <t>2026-09-18 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1527,12 +1335,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1548,62 +1356,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/falkenbergs-vs-ostersunds-fk/1636382438</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00</t>
+          <t>2026-09-18 17:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.460</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.640</t>
+          <t>3.020</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1611,17 +1419,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1637,12 +1445,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/uta-arad-vs-sepsi/1636346520</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-arges-pitesti/1636378753</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00</t>
+          <t>2026-09-18 18:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1652,22 +1460,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Rapid Bucuresti</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.645</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1677,22 +1485,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.110</t>
+          <t>5.390</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1700,17 +1508,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1726,47 +1534,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30</t>
+          <t>2026-09-18 18:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1776,12 +1584,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1789,17 +1597,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1815,62 +1623,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30</t>
+          <t>2026-09-18 18:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.440</t>
+          <t>2.410</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1878,17 +1686,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1904,62 +1712,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-18 22:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>6.760</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1967,12 +1775,12 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1993,62 +1801,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-inter-turku/1636378694</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ceara-vs-gremio-novorizontino/1636385559</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2061,12 +1869,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2082,62 +1890,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/widzew-lodz-vs-wieczysta-krakow/1636378696</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-19 00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.360</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2145,17 +1953,17 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2171,12 +1979,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-19 10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2186,32 +1994,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2221,12 +2029,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2234,17 +2042,17 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2260,12 +2068,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/falkenbergs-vs-ostersunds-fk/1636382438</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00</t>
+          <t>2026-09-19 11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2275,47 +2083,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.370</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2323,17 +2131,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2349,62 +2157,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-arges-pitesti/1636378753</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-landskrona/1636434678</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-18 18:00</t>
+          <t>2026-09-19 11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rapid Bucuresti</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.960</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2412,17 +2220,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2438,47 +2246,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-18 18:30</t>
+          <t>2026-09-19 12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.590</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2488,12 +2296,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2501,17 +2309,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2527,62 +2335,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-sociedad-ii-vs-mallorca/1636442645</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-18 18:30</t>
+          <t>2026-09-19 12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.680</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2590,17 +2398,17 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2616,62 +2424,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/korona-kielce-vs-rakow-czestochowa/1636442668</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45</t>
+          <t>2026-09-19 12:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.410</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2684,12 +2492,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2705,62 +2513,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-18 22:30</t>
+          <t>2026-09-19 13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.580</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2768,17 +2576,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2794,62 +2602,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-brage/1636454979</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-19 13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2857,17 +2665,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2883,62 +2691,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-jippo/1636581425</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-19 10:30</t>
+          <t>2026-09-19 13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>1.684</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2946,17 +2754,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2972,62 +2780,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-lks-lodz/1635909034</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-19 12:00</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3040,12 +2848,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -3061,62 +2869,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-sociedad-ii-vs-mallorca/1636442645</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-19 12:00</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3124,17 +2932,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3150,62 +2958,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-jippo/1636581425</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-19 13:00</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3213,17 +3021,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3239,62 +3047,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-kups/1636463837</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3302,17 +3110,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3328,62 +3136,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-lks-lodz/1635909034</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-vs-bryne/1636463898</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3391,17 +3199,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3417,62 +3225,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-ktp/1636463842</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.990</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3480,17 +3288,17 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3506,62 +3314,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-kups/1636463837</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/fc-andorra-vs-sporting-gijon/1636463851</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00</t>
+          <t>2026-09-19 14:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3574,12 +3382,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3595,62 +3403,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-vs-bryne/1636463898</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/cfr-cluj-vs-botosani/1636480675</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00</t>
+          <t>2026-09-19 14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3658,17 +3466,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3684,62 +3492,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-ktp/1636463842</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-orebro-sk/1636480694</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00</t>
+          <t>2026-09-19 15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.620</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3752,12 +3560,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3773,62 +3581,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/fc-andorra-vs-sporting-gijon/1636463851</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-19 14:15</t>
+          <t>2026-09-19 15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.360</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3836,17 +3644,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3862,62 +3670,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/cfr-cluj-vs-botosani/1636480675</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-19 14:30</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -3925,17 +3733,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -3951,42 +3759,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>2.930</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4001,12 +3809,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4014,17 +3822,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4040,62 +3848,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>5.530</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4108,12 +3916,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -4129,62 +3937,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/miedz-legnica-vs-stal-rzeszow/1635909114</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>4.210</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>4.670</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -4192,17 +4000,17 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -4218,62 +4026,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-craiova-vs-fcsb/1636486507</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-19 17:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.530</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -4281,17 +4089,17 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -4307,62 +4115,62 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/miedz-legnica-vs-stal-rzeszow/1635909114</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/motor-lublin-vs-gornik-zabrze/1636498723</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-19 18:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stal Rzeszow</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -4370,17 +4178,17 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4396,62 +4204,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-craiova-vs-fcsb/1636486507</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cadiz-vs-girona/1636486543</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-19 17:30</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>2.010</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.800</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -4459,17 +4267,17 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
@@ -4485,62 +4293,62 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cadiz-vs-girona/1636486543</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sport-recife-vs-juventude/1636498734</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -4548,17 +4356,17 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -4599,12 +4407,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.370</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4614,7 +4422,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4624,12 +4432,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -4642,12 +4450,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
@@ -4688,7 +4496,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4752,7 +4560,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/voluntari-vs-universitatea-cluj/1636537327</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ljungskile/1636537335</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4762,52 +4570,52 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -4820,12 +4628,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -4841,62 +4649,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sabadell-vs-real-oviedo/1636554000</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/voluntari-vs-universitatea-cluj/1636537327</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-20 12:00</t>
+          <t>2026-09-20 11:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:40</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.990</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -4904,17 +4712,17 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -4930,62 +4738,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-siedlce-vs-arka-gdynia/1635909115</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sabadell-vs-real-oviedo/1636554000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-20 12:30</t>
+          <t>2026-09-20 12:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>2.990</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -4993,12 +4801,12 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5019,62 +4827,62 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/helsingborgs-vs-norrby/1636554051</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-siedlce-vs-arka-gdynia/1635909115</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-20 13:00</t>
+          <t>2026-09-20 12:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -5082,17 +4890,17 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
@@ -5108,47 +4916,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-valladolid/1636569764</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/zaglebie-lubin-vs-wisla-plock/1636554036</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15</t>
+          <t>2026-09-20 12:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.900</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>2.830</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5158,12 +4966,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -5176,12 +4984,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
@@ -5197,47 +5005,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/helsingborgs-vs-norrby/1636554051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-20 13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5247,12 +5055,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -5260,17 +5068,17 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
@@ -5286,47 +5094,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-crb/1636554091</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-20 14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7.930</t>
+          <t>9.820</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6.090</t>
+          <t>5.660</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.264</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5336,12 +5144,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -5349,17 +5157,17 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
@@ -5375,62 +5183,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-valladolid/1636569764</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-20 14:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>2.790</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.510</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>2.520</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -5438,17 +5246,17 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -5464,7 +5272,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5479,47 +5287,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6.380</t>
+          <t>5.350</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8.000</t>
+          <t>5.860</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -5532,12 +5340,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
@@ -5553,7 +5361,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5568,47 +5376,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5.330</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.850</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -5616,17 +5424,17 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -5642,7 +5450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5657,47 +5465,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5.530</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>9.000</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -5705,17 +5513,17 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
@@ -5731,7 +5539,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5746,47 +5554,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>5.640</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>9.300</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -5794,17 +5602,17 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -5820,62 +5628,62 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-legia-warsaw/1636498762</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>7.930</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>6.090</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2.370</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+1.75</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -5883,17 +5691,17 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -5909,62 +5717,62 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-unia-skierniewice/1635909033</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-20 15:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Podbeskidzie Bielsko-Biala</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>6.430</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>8.100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -5972,17 +5780,17 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -5998,62 +5806,62 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47</t>
+          <t>2026-09-16 10:38</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.940</t>
+          <t>4.580</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7.430</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -6061,17 +5869,17 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S61" t="inlineStr"/>
@@ -6087,62 +5895,62 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-legia-warsaw/1636498762</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-20 16:30</t>
+          <t>2026-09-20 15:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.940</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -6150,17 +5958,17 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S62" t="inlineStr"/>
@@ -6176,62 +5984,62 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/dinamo-bucuresti-vs-farul-constanta/1636572912</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-unia-skierniewice/1635909033</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-20 17:30</t>
+          <t>2026-09-20 15:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Dinamo Bucuresti</t>
+          <t>Podbeskidzie Bielsko-Biala</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5.030</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -6239,17 +6047,17 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S63" t="inlineStr"/>
@@ -6265,62 +6073,62 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/lech-poznan-vs-radomiak-radom/1636498768</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15</t>
+          <t>2026-09-20 16:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6.070</t>
+          <t>3.020</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8.680</t>
+          <t>4.450</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -6328,17 +6136,17 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S64" t="inlineStr"/>
@@ -6354,12 +6162,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-granada/1636572929</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-20 19:00</t>
+          <t>2026-09-20 16:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6369,47 +6177,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-15 10:48</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.377</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>5.050</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>7.480</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -6417,17 +6225,17 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6443,62 +6251,62 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-avai/1636578432</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/dinamo-bucuresti-vs-farul-constanta/1636572912</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-20 19:00</t>
+          <t>2026-09-20 17:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Dinamo Bucuresti</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-15 10:49</t>
+          <t>2026-09-16 10:40</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4.590</t>
+          <t>5.040</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -6506,17 +6314,17 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S66" t="inlineStr"/>
@@ -6532,62 +6340,62 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/otelul-galati-vs-corvinul-hunedoara/1636611974</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/lech-poznan-vs-radomiak-radom/1636498768</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00</t>
+          <t>2026-09-20 18:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:39</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>1.280</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>5.900</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>8.370</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -6595,17 +6403,17 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S67" t="inlineStr"/>
@@ -6621,62 +6429,62 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-granada/1636572929</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-21 18:00</t>
+          <t>2026-09-20 19:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-15 10:50</t>
+          <t>2026-09-16 10:37</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4.850</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -6689,12 +6497,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
           <t>1.781</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>2.020</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
@@ -6707,6 +6515,451 @@
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-avai/1636578432</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:38</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>4.590</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-fortaleza/1636572953</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-20 21:30</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:38</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>3.190</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2.990</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2.460</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-21 18:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Romania - Liga 1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Petrolul Ploiesti</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Csikszereda</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:40</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.680</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3.710</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4.930</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1636636585</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Operario Ferroviario</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:38</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3.380</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4.930</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-nautico/1636640777</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-22 00:30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Nautico</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:39</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3.210</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3.770</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,47 +570,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:36</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>4.370</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.360</t>
+          <t>5.420</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -623,12 +623,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -644,7 +644,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -659,47 +659,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:36</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.430</t>
+          <t>4.330</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -758,22 +758,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>4.290</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -801,12 +801,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -847,37 +847,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>2.360</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -890,12 +890,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -979,12 +979,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-inter-turku/1636378694</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1015,32 +1015,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16 10:36</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1063,17 +1063,17 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-inter-turku/1636378694</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1104,32 +1104,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-16 10:36</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1152,17 +1152,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1241,17 +1241,17 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.980</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1292,17 +1292,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1559,17 +1559,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1597,17 +1597,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1623,62 +1623,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45</t>
+          <t>2026-09-18 18:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>1.632</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.410</t>
+          <t>4.680</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1686,17 +1686,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1712,62 +1712,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-18 22:30</t>
+          <t>2026-09-18 18:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.760</t>
+          <t>2.410</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1775,17 +1775,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1801,12 +1801,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ceara-vs-gremio-novorizontino/1636385559</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-18 22:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1816,47 +1816,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.900</t>
+          <t>1.456</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>7.400</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1864,17 +1864,17 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1890,12 +1890,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ceara-vs-gremio-novorizontino/1636385559</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1905,47 +1905,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1979,62 +1979,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-19 10:30</t>
+          <t>2026-09-19 00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>2.890</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2042,17 +2042,17 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2068,62 +2068,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-19 11:00</t>
+          <t>2026-09-19 10:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2131,17 +2131,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2182,22 +2182,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2246,62 +2246,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-19 12:00</t>
+          <t>2026-09-19 11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2309,17 +2309,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-brage/1636454979</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2528,47 +2528,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2602,7 +2602,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-brage/1636454979</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.500</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2869,7 +2869,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2932,17 +2932,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3021,17 +3021,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3695,22 +3695,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -3784,37 +3784,37 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.930</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3873,22 +3873,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.530</t>
+          <t>5.590</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3911,17 +3911,17 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4051,22 +4051,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-16 10:40</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4407,17 +4407,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4585,22 +4585,22 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-16 10:40</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -4763,22 +4763,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.990</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.830</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -5030,22 +5030,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -5068,17 +5068,17 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
@@ -5119,37 +5119,37 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9.820</t>
+          <t>9.480</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.660</t>
+          <t>5.590</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.284</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>+1.75</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
@@ -5208,22 +5208,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:46</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>2.640</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>2.700</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -5272,7 +5272,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5287,47 +5287,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>7.930</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5.350</t>
+          <t>6.090</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5.860</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>+1.75</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -5335,17 +5335,17 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5376,47 +5376,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>6.290</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>7.820</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -5424,17 +5424,17 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5465,47 +5465,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>5.360</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>5.880</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -5513,7 +5513,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
@@ -5564,37 +5564,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5.640</t>
+          <t>5.560</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>9.300</t>
+          <t>9.080</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -5628,7 +5628,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5643,47 +5643,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.930</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6.090</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>+1.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -5691,17 +5691,17 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -5717,7 +5717,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5732,47 +5732,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6.430</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8.100</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -5780,17 +5780,17 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6073,7 +6073,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6088,47 +6088,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3.020</t>
+          <t>4.910</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4.450</t>
+          <t>7.360</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -6136,17 +6136,17 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S64" t="inlineStr"/>
@@ -6162,7 +6162,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6177,47 +6177,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5.050</t>
+          <t>3.020</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>7.480</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -6225,17 +6225,17 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6276,22 +6276,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-16 10:40</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1.606</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5.040</t>
+          <t>5.060</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S66" t="inlineStr"/>
@@ -6365,22 +6365,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.280</t>
+          <t>1.290</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.900</t>
+          <t>5.790</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8.370</t>
+          <t>8.160</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S67" t="inlineStr"/>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-16 10:37</t>
+          <t>2026-09-17 10:47</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6543,22 +6543,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4.590</t>
+          <t>4.630</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -6586,12 +6586,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6696,12 +6696,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/otelul-galati-vs-corvinul-hunedoara/1636611974</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-21 18:00</t>
+          <t>2026-09-21 15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6711,47 +6711,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-16 10:40</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4.930</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -6759,17 +6759,17 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S71" t="inlineStr"/>
@@ -6785,42 +6785,42 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1636636585</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30</t>
+          <t>2026-09-21 18:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Petrolul Ploiesti</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-16 10:38</t>
+          <t>2026-09-17 10:49</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.680</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -6848,17 +6848,17 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S72" t="inlineStr"/>
@@ -6874,12 +6874,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-nautico/1636640777</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1636636585</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-22 00:30</t>
+          <t>2026-09-21 22:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6889,47 +6889,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39</t>
+          <t>2026-09-17 10:48</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>4.930</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -6942,12 +6942,12 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S73" t="inlineStr"/>
@@ -6960,6 +6960,95 @@
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-nautico/1636640777</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-22 00:30</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Nautico</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:48</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>3.240</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3.860</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,12 +580,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.420</t>
+          <t>5.450</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,35 +605,59 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -669,42 +693,54 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.330</t>
+          <t>4.230</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -712,17 +748,29 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -758,60 +806,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.350</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3.580</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>1.793</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3.640</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4.290</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -822,7 +894,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -837,70 +909,94 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>1.478</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>4.930</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>5.650</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -911,7 +1007,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -926,70 +1022,94 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.456</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.800</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.560</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1000,7 +1120,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-inter-turku/1636378694</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1015,70 +1135,94 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>4.330</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>4.240</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1089,7 +1233,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/widzew-lodz-vs-wieczysta-krakow/1636378696</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1099,57 +1243,69 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>4.210</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>3</t>
@@ -1157,17 +1313,29 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1178,7 +1346,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/widzew-lodz-vs-wieczysta-krakow/1636378696</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,75 +1356,99 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1267,47 +1459,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/falkenbergs-vs-ostersunds-fk/1636382438</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-18 17:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1317,35 +1509,59 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1356,85 +1572,109 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/falkenbergs-vs-ostersunds-fk/1636382438</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-arges-pitesti/1636378753</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00</t>
+          <t>2026-09-18 18:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Rapid Bucuresti</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>1.568</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.020</t>
+          <t>6.320</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1445,85 +1685,109 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-arges-pitesti/1636378753</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-18 18:00</t>
+          <t>2026-09-18 18:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rapid Bucuresti</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.645</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.390</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1534,7 +1798,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1544,75 +1808,99 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>5.130</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1623,85 +1911,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-18 18:30</t>
+          <t>2026-09-18 18:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>2.800</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.680</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1712,85 +2024,109 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45</t>
+          <t>2026-09-18 22:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.410</t>
+          <t>8.390</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1801,12 +2137,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ceara-vs-gremio-novorizontino/1636385559</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-18 22:30</t>
+          <t>2026-09-18 23:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1816,70 +2152,94 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.456</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.400</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -1890,12 +2250,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ceara-vs-gremio-novorizontino/1636385559</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-19 00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1905,52 +2265,64 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>2.790</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1958,17 +2330,29 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1979,62 +2363,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-19 10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.890</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2042,17 +2426,17 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2068,85 +2452,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-landskrona/1636434678</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-19 10:30</t>
+          <t>2026-09-19 11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>2.310</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3.590</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.840</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>2.030</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3.750</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3.240</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2157,7 +2565,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-landskrona/1636434678</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2172,70 +2580,94 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2246,85 +2678,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-19 11:00</t>
+          <t>2026-09-19 12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>2.590</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2360,22 +2816,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2385,12 +2841,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2403,7 +2859,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2449,22 +2905,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2474,7 +2930,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2482,9 +2938,21 @@
           <t>2.000</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -2492,7 +2960,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2500,9 +2968,21 @@
           <t>1.813</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.757</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2513,7 +2993,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-brage/1636454979</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2528,52 +3008,64 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.500</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -2581,17 +3073,29 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2602,7 +3106,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-brage/1636454979</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2617,52 +3121,64 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>4.210</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>4.910</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -2670,17 +3186,29 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -2716,22 +3244,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>4.130</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2741,35 +3269,59 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -2805,22 +3357,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>2.160</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2830,35 +3382,59 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -2894,7 +3470,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2919,12 +3495,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2937,12 +3513,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2983,60 +3559,84 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.590</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3.690</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.690</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4.070</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3072,22 +3672,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3097,17 +3697,29 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -3115,17 +3727,29 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3161,7 +3785,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3171,12 +3795,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3186,12 +3810,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3199,17 +3823,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3250,7 +3874,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3260,12 +3884,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3275,7 +3899,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3283,9 +3907,21 @@
           <t>1.917</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3293,17 +3929,29 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -3339,7 +3987,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3349,7 +3997,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3369,12 +4017,24 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -3382,17 +4042,29 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -3403,85 +4075,109 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/cfr-cluj-vs-botosani/1636480675</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-orebro-sk/1636480694</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-19 14:30</t>
+          <t>2026-09-19 15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -3492,7 +4188,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-orebro-sk/1636480694</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3502,57 +4198,69 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>2.680</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3560,17 +4268,29 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -3581,67 +4301,79 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3649,17 +4381,29 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -3670,85 +4414,109 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-fylkir/1636611964</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-19 16:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>1.813</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -3759,7 +4527,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3774,47 +4542,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>1.549</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.050</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>5.740</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -3822,17 +4590,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3848,7 +4616,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3863,47 +4631,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.590</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3911,17 +4679,17 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -3962,22 +4730,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.657</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>4.140</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>4.400</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3987,17 +4755,29 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>3</t>
@@ -4005,17 +4785,29 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -4051,22 +4843,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.980</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>4.350</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4076,17 +4868,29 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>3</t>
@@ -4094,17 +4898,29 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -4140,22 +4956,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4165,17 +4981,29 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -4183,17 +5011,29 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
@@ -4229,7 +5069,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4254,12 +5094,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -4272,12 +5112,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
@@ -4318,22 +5158,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4343,35 +5183,59 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>2.080</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -4407,7 +5271,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4432,17 +5296,29 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>2</t>
@@ -4450,17 +5326,29 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -4496,17 +5384,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4521,17 +5409,29 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -4539,17 +5439,29 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -4585,7 +5497,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4618,9 +5530,21 @@
           <t>1.884</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -4636,9 +5560,21 @@
           <t>1.934</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
@@ -4674,7 +5610,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4707,9 +5643,21 @@
           <t>1.826</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -4725,9 +5673,21 @@
           <t>1.847</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -4763,22 +5723,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>2.940</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4788,12 +5748,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -4801,17 +5761,17 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
@@ -4852,7 +5812,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4941,22 +5901,22 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4966,17 +5926,29 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -4984,17 +5956,29 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
@@ -5030,7 +6014,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5063,9 +6047,21 @@
           <t>1.961</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -5081,9 +6077,21 @@
           <t>2.010</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
@@ -5119,17 +6127,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9.480</t>
+          <t>9.260</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.590</t>
+          <t>5.670</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5144,17 +6152,29 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>3</t>
@@ -5162,17 +6182,29 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -5208,22 +6240,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-17 10:46</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2.700</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5233,35 +6265,59 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -5272,7 +6328,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5287,70 +6343,94 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.930</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6.090</t>
+          <t>6.290</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>7.820</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+1.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -5361,7 +6441,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5376,70 +6456,94 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6.290</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7.820</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
@@ -5450,7 +6554,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5465,70 +6569,94 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5.360</t>
+          <t>4.780</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5.880</t>
+          <t>4.030</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>1.813</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -5539,7 +6667,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5554,70 +6682,94 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>7.930</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6.090</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>1.271</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>5.560</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>9.080</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>+1.75</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -5628,7 +6780,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5643,55 +6795,67 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>5.360</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>5.880</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5701,12 +6865,24 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
@@ -5742,7 +6918,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5775,9 +6951,21 @@
           <t>1.892</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -5793,9 +6981,21 @@
           <t>1.862</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
@@ -5806,7 +7006,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5821,52 +7021,64 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.276</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.580</t>
+          <t>5.520</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>9.010</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>4</t>
@@ -5874,17 +7086,29 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -5920,22 +7144,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>2.370</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5945,17 +7169,29 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -5971,9 +7207,21 @@
           <t>1.877</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
@@ -6009,7 +7257,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6073,7 +7321,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6088,70 +7336,94 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.910</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7.360</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
@@ -6162,7 +7434,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6177,47 +7449,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.020</t>
+          <t>4.970</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>7.360</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -6225,17 +7497,17 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6276,7 +7548,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6365,22 +7637,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.290</t>
+          <t>1.293</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.790</t>
+          <t>5.750</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8.160</t>
+          <t>8.140</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6390,17 +7662,29 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -6408,17 +7692,29 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
@@ -6454,22 +7750,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-17 10:47</t>
+          <t>2026-09-18 10:21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6479,35 +7775,59 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
@@ -6543,7 +7863,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6576,9 +7896,21 @@
           <t>1.961</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>2</t>
@@ -6594,9 +7926,21 @@
           <t>2.010</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
@@ -6632,60 +7976,84 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>2.880</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2.990</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>2.080</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
@@ -6721,7 +8089,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6731,12 +8099,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6751,7 +8119,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -6764,12 +8132,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S71" t="inlineStr"/>
@@ -6810,7 +8178,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-17 10:49</t>
+          <t>2026-09-18 10:24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6843,9 +8211,21 @@
           <t>1.909</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -6861,9 +8241,21 @@
           <t>1.813</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
@@ -6899,22 +8291,22 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.699</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4.930</t>
+          <t>5.370</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6924,17 +8316,29 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -6942,17 +8346,29 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
@@ -6988,7 +8404,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-17 10:48</t>
+          <t>2026-09-18 10:22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7021,9 +8437,21 @@
           <t>1.793</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -7039,9 +8467,21 @@
           <t>1.826</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-jaro/1636346519</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00</t>
+          <t>2026-09-19 10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,62 +668,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-ifk-mariehamn/1636346518</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00</t>
+          <t>2026-09-19 11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -733,42 +733,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/uta-arad-vs-sepsi/1636346520</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-landskrona/1636434678</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00</t>
+          <t>2026-09-19 11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>2.730</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,107 +894,107 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-hjk-klubi-04/1636333053</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30</t>
+          <t>2026-09-19 12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.930</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.650</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,37 +1007,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-eif/1636341526</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-sociedad-ii-vs-mallorca/1636442645</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30</t>
+          <t>2026-09-19 12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1067,32 +1067,32 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,107 +1120,107 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-hjk-helsinki/1636346549</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/korona-kielce-vs-rakow-czestochowa/1636442668</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-19 12:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.330</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.240</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>3.110</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>1.757</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,92 +1233,92 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/widzew-lodz-vs-wieczysta-krakow/1636378696</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-19 13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>2.220</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.570</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3.150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.210</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3.540</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,62 +1346,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-puszcza-niepolomice/1636378695</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-jippo/1636581425</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00</t>
+          <t>2026-09-19 13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1411,42 +1411,42 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/falkenbergs-vs-ostersunds-fk/1636382438</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-lks-lodz/1635909034</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.380</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>1.925</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.793</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,107 +1572,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/rapid-bucuresti-vs-arges-pitesti/1636378753</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-18 18:00</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rapid Bucuresti</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.568</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.320</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,77 +1685,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/albacete-vs-cordoba/1636385511</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-18 18:30</t>
+          <t>2026-09-19 13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1765,27 +1765,27 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,52 +1798,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wisla-krakow-vs-slask-wroclaw/1636378772</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-kups/1636463837</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-18 18:30</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.130</t>
+          <t>2.160</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1853,52 +1853,52 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>1.854</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.862</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,62 +1911,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-bytom-vs-ruch-chorzow/1636382504</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-vs-bryne/1636463898</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-18 18:45</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1991,27 +1991,27 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,62 +2024,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-america-mineiro/1636385547</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-ktp/1636463842</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-18 22:30</t>
+          <t>2026-09-19 14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8.390</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2089,42 +2089,42 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,107 +2137,107 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ceara-vs-gremio-novorizontino/1636385559</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/fc-andorra-vs-sporting-gijon/1636463851</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-18 23:30</t>
+          <t>2026-09-19 14:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2250,107 +2250,107 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-atletico-goianiense/1636385562</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/cfr-cluj-vs-botosani/1636480675</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-19 00:00</t>
+          <t>2026-09-19 14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2363,85 +2363,109 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lechia-gdansk-vs-stal-mielec/1635909038</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-orebro-sk/1636480694</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-19 10:30</t>
+          <t>2026-09-19 15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2452,77 +2476,77 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-landskrona/1636434678</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-19 11:00</t>
+          <t>2026-09-19 15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.840</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2532,12 +2556,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2547,12 +2571,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2565,107 +2589,107 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/osters-vs-norrkoping/1636434677</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-19 11:00</t>
+          <t>2026-09-19 15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>3.100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>1.793</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.869</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2678,107 +2702,107 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ilves/1636439257</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-fylkir/1636611964</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-19 12:00</t>
+          <t>2026-09-19 16:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>4.040</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>3.670</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2.550</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2791,12 +2815,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-sociedad-ii-vs-mallorca/1636442645</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-19 12:00</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2806,70 +2830,94 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>6.850</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2880,62 +2928,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/korona-kielce-vs-rakow-czestochowa/1636442668</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-19 12:45</t>
+          <t>2026-09-19 16:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2945,27 +2993,27 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2975,12 +3023,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -2993,107 +3041,107 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/oddevold-vs-varnamo/1636463784</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/miedz-legnica-vs-stal-rzeszow/1635909114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-19 13:00</t>
+          <t>2026-09-19 17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>4.270</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>4.520</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>1.884</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.943</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3106,77 +3154,77 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-brage/1636454979</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-craiova-vs-fcsb/1636486507</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-19 13:00</t>
+          <t>2026-09-19 17:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.910</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3186,12 +3234,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3201,12 +3249,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3219,107 +3267,107 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-jippo/1636581425</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/motor-lublin-vs-gornik-zabrze/1636498723</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-19 13:00</t>
+          <t>2026-09-19 18:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4.130</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3332,107 +3380,107 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-lks-lodz/1635909034</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cadiz-vs-girona/1636486543</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30</t>
+          <t>2026-09-19 19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.160</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -3445,85 +3493,109 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/nieciecza-vs-odra-opole/1635909035</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sport-recife-vs-juventude/1636498734</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30</t>
+          <t>2026-09-19 19:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3534,107 +3606,107 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/polonia-warsaw-vs-chrobry-glogow/1635909036</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-pogon-szczecin/1636498184</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30</t>
+          <t>2026-09-20 10:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>2.950</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3647,107 +3719,107 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-kups/1636463837</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ljungskile/1636537335</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00</t>
+          <t>2026-09-20 11:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -3760,85 +3832,109 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-vs-bryne/1636463898</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/voluntari-vs-universitatea-cluj/1636537327</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00</t>
+          <t>2026-09-20 11:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
           <t>+0.5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3849,107 +3945,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-ktp/1636463842</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sabadell-vs-real-oviedo/1636554000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00</t>
+          <t>2026-09-20 12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.990</t>
+          <t>2.410</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>2.890</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -3962,79 +4058,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/fc-andorra-vs-sporting-gijon/1636463851</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-siedlce-vs-arka-gdynia/1635909115</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-19 14:15</t>
+          <t>2026-09-20 12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -4042,29 +4126,17 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -4075,62 +4147,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-orebro-sk/1636480694</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/zaglebie-lubin-vs-wisla-plock/1636554036</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00</t>
+          <t>2026-09-20 12:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4140,42 +4212,42 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4188,79 +4260,79 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-kapa/1636483868</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/helsingborgs-vs-norrby/1636554051</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00</t>
+          <t>2026-09-20 13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -4273,17 +4345,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4301,62 +4373,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-cracovia-krakow/1636483889</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-crb/1636554091</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30</t>
+          <t>2026-09-20 14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>9.260</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.620</t>
+          <t>5.670</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>1.284</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4366,17 +4438,17 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4386,22 +4458,22 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -4414,107 +4486,107 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-fylkir/1636611964</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-valladolid/1636569764</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-19 16:15</t>
+          <t>2026-09-20 14:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>1.813</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1.900</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4527,85 +4599,109 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/castellon-vs-tenerife/1636483918</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.740</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
@@ -4616,85 +4712,109 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eldense-vs-eibar/1636486482</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>5.360</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>5.880</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
@@ -4705,47 +4825,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/miedz-legnica-vs-stal-rzeszow/1635909114</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stal Rzeszow</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.657</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4755,12 +4875,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4770,27 +4890,27 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4800,12 +4920,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -4818,107 +4938,107 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/universitatea-craiova-vs-fcsb/1636486507</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-19 17:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-18 10:24</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>5.810</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.350</t>
+          <t>6.940</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -4931,107 +5051,107 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/motor-lublin-vs-gornik-zabrze/1636498723</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>5.560</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>9.090</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -5044,85 +5164,109 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/cadiz-vs-girona/1636486543</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-19 19:00</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>7.930</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>6.090</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.75</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -5133,107 +5277,107 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sport-recife-vs-juventude/1636498734</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30</t>
+          <t>2026-09-20 15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>4.700</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.920</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -5246,82 +5390,82 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-botafogo-sp/1636506150</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-legia-warsaw/1636498762</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30</t>
+          <t>2026-09-20 15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5331,22 +5475,22 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -5359,52 +5503,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-pogon-szczecin/1636498184</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-unia-skierniewice/1635909033</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-20 10:15</t>
+          <t>2026-09-20 15:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Podbeskidzie Bielsko-Biala</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5414,54 +5558,30 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>2.020</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -5472,107 +5592,107 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ljungskile/1636537335</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-20 11:00</t>
+          <t>2026-09-20 16:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>4.370</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
         <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>1.854</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>1.869</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -5585,107 +5705,107 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/voluntari-vs-universitatea-cluj/1636537327</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-20 11:00</t>
+          <t>2026-09-20 16:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-18 10:24</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>4.930</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>7.300</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5698,85 +5818,109 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sabadell-vs-real-oviedo/1636554000</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/dinamo-bucuresti-vs-farul-constanta/1636572912</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-20 12:00</t>
+          <t>2026-09-20 17:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Dinamo Bucuresti</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.380</t>
+          <t>1.606</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.940</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>5.060</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>1.781</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -5787,85 +5931,109 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-siedlce-vs-arka-gdynia/1635909115</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/lech-poznan-vs-radomiak-radom/1636498768</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-20 12:30</t>
+          <t>2026-09-20 18:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>5.720</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>8.150</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -5876,107 +6044,107 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/zaglebie-lubin-vs-wisla-plock/1636554036</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-granada/1636572929</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-20 12:45</t>
+          <t>2026-09-20 19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-18 10:23</t>
+          <t>2026-09-19 10:04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>1.787</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1.847</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -5989,62 +6157,62 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/helsingborgs-vs-norrby/1636554051</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-avai/1636578432</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-20 13:00</t>
+          <t>2026-09-20 19:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>4.630</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6054,42 +6222,42 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
         <is>
           <t>1.787</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -6102,12 +6270,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-crb/1636554091</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-fortaleza/1636572953</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-20 14:00</t>
+          <t>2026-09-20 21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6117,92 +6285,92 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9.260</t>
+          <t>2.890</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.670</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>2.640</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="V53" t="inlineStr"/>
@@ -6215,109 +6383,85 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-valladolid/1636569764</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/otelul-galati-vs-corvinul-hunedoara/1636611974</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-20 14:15</t>
+          <t>2026-09-21 15:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-18 10:21</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -6328,87 +6472,87 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-strommen/1636498754</t>
+          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-21 18:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Romania - Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Petrolul Ploiesti</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6.290</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>7.820</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6418,17 +6562,17 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V55" t="inlineStr"/>
@@ -6441,107 +6585,107 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-moss/1636498198</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1636636585</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-21 22:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>5.250</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
           <t>1.847</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>1.909</t>
         </is>
       </c>
       <c r="V56" t="inlineStr"/>
@@ -6554,92 +6698,92 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-ranheim/1636506140</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-nautico/1636640777</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-22 00:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.780</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4.030</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6649,12 +6793,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -6667,109 +6811,85 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-stromsgodset/1636498763</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-20 15:00</t>
+          <t>2026-09-25 22:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-18 10:22</t>
+          <t>2026-09-19 10:06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7.930</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6.090</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>5.860</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>+1.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -6777,1718 +6897,6 @@
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-sogndal/1636532662</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-20 15:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Norway - 1st Division</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Stabaek</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Sogndal</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>5.360</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5.880</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-egersunds/1636498750</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-20 15:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Norway - 1st Division</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Odd BK</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Egersunds</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1.714</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>4.310</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3.940</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-hodd/1636506138</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-20 15:00</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Norway - 1st Division</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Kongsvinger</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Hodd</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>1.276</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>5.520</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>9.010</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-legia-warsaw/1636498762</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-20 15:30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Poland - Ekstraklasa</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Jagiellonia Bialystok</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Legia Warsaw</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:23</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2.920</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>3.430</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2.370</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-unia-skierniewice/1635909033</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-20 15:30</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Poland - 1st Liga</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Podbeskidzie Bielsko-Biala</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Unia Skierniewice</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:23</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>3.680</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3.210</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/las-palmas-vs-burgos/1636569840</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-20 16:30</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Spain - Segunda</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:21</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2.980</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>4.300</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/almeria-vs-celta-vigo-ii/1636569839</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-20 16:30</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Spain - Segunda</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Almeria</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Celta Vigo II</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:21</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1.387</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>4.970</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7.360</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/dinamo-bucuresti-vs-farul-constanta/1636572912</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-20 17:30</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Romania - Liga 1</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Dinamo Bucuresti</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Farul Constanta</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:24</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>1.606</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>4.040</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5.060</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/lech-poznan-vs-radomiak-radom/1636498768</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-20 18:15</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Poland - Ekstraklasa</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Lech Poznan</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Radomiak Radom</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:23</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>1.293</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>5.750</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8.140</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-granada/1636572929</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-20 19:00</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Spain - Segunda</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:21</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>3.150</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3.980</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-avai/1636578432</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-20 19:00</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Avai</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>3.260</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4.630</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-fortaleza/1636572953</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-09-20 21:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2.880</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>3.030</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2.650</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/otelul-galati-vs-corvinul-hunedoara/1636611974</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-09-21 15:00</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Romania - Liga 1</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Otelul Galati</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Corvinul Hunedoara</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:24</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2.420</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>3.140</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3.040</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-09-21 18:00</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Romania - Liga 1</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Petrolul Ploiesti</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Csikszereda</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:24</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>1.680</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>3.710</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>4.930</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1636636585</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-09-21 22:30</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Criciuma</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Operario Ferroviario</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>1.699</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>3.490</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5.370</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-nautico/1636640777</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-09-22 00:30</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Cuiaba</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-09-18 10:22</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>3.240</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3.860</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/otelul-galati-vs-corvinul-hunedoara/1636611974</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1637175360</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00</t>
+          <t>2026-09-22 22:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>4.350</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,109 +668,85 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/romania-liga-1/petrolul-ploiesti-vs-csikszereda/1636618551</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-mikkelin-palloilijat/1636953757</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 18:00</t>
+          <t>2026-09-25 15:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania - Liga 1</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>5.100</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.810</t>
+          <t>6.760</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -781,109 +757,85 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1636636585</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-fc-haka/1636953776</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30</t>
+          <t>2026-09-25 16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>5.660</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>4.650</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.770</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -894,109 +846,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-nautico/1636640777</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22 00:30</t>
+          <t>2026-09-25 18:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>1.510</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>4.550</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>5.720</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1007,62 +935,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-mikkelin-palloilijat/1636953757</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:30</t>
+          <t>2026-09-25 22:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-21 11:41</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1.549</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.200</t>
+          <t>4.060</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.010</t>
+          <t>5.870</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1070,17 +998,17 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1096,47 +1024,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-25 18:30</t>
+          <t>2026-09-25 23:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-21 11:40</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.700</t>
+          <t>6.280</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1146,12 +1074,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1159,17 +1087,17 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1185,62 +1113,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25 22:30</t>
+          <t>2026-09-26 12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.830</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1248,17 +1176,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1274,62 +1202,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-25 23:30</t>
+          <t>2026-09-26 12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.671</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>4.410</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.280</t>
+          <t>4.060</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1337,17 +1265,17 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1363,62 +1291,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-26 13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-21 11:40</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>2.800</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1426,17 +1354,17 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>2.010</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1452,62 +1380,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-26 14:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.060</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1515,17 +1443,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1541,12 +1469,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 13:00</t>
+          <t>2026-09-26 16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1556,47 +1484,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.380</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1604,17 +1532,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1630,12 +1558,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 14:15</t>
+          <t>2026-09-26 16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1645,47 +1573,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21 11:40</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>4.740</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1693,17 +1621,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1719,57 +1647,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00</t>
+          <t>2026-09-26 16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.080</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1782,17 +1710,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1808,62 +1736,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-sport-recife/1637098349</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-26 19:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-21 11:40</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.150</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.740</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1871,17 +1799,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1897,62 +1825,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-26 21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-21 11:41</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>2.880</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.740</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1960,17 +1888,17 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1986,47 +1914,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30</t>
+          <t>2026-09-27 12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.410</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.900</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2036,12 +1964,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2049,17 +1977,17 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2075,12 +2003,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00</t>
+          <t>2026-09-27 14:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2090,47 +2018,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:41</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2143,12 +2071,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2164,12 +2092,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15</t>
+          <t>2026-09-27 16:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2179,32 +2107,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-21 11:41</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>4.200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2214,12 +2142,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2227,17 +2155,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>1.970</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.869</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2253,7 +2181,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2268,32 +2196,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-21 11:41</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>4.130</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2303,12 +2231,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2316,17 +2244,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2367,22 +2295,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-21 11:41</t>
+          <t>2026-09-22 10:46</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2392,12 +2320,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2410,12 +2338,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2456,7 +2384,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-21 11:42</t>
+          <t>2026-09-22 10:47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2517,6 +2445,184 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Spain - Segunda</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:46</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3.340</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.270</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2.250</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:47</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3.470</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.360</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.130</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,57 +555,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-operario-ferroviario/1637175360</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-mikkelin-palloilijat/1636953757</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 22:30</t>
+          <t>2026-09-25 15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>5.360</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.350</t>
+          <t>6.890</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -613,51 +613,27 @@
           <t>1.869</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -668,12 +644,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-mikkelin-palloilijat/1636953757</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-fc-haka/1636953776</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:30</t>
+          <t>2026-09-25 16:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,47 +659,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>5.450</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.100</t>
+          <t>4.600</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.760</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>1.800</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2.020</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -736,12 +712,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -757,85 +733,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-fc-haka/1636953776</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 16:00</t>
+          <t>2026-09-25 18:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.660</t>
+          <t>1.549</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.650</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>5.460</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -846,47 +846,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 18:30</t>
+          <t>2026-09-25 22:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-22 10:45</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.510</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.550</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.720</t>
+          <t>5.740</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -909,17 +909,17 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -935,12 +935,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25 22:30</t>
+          <t>2026-09-25 23:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,47 +950,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.060</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.870</t>
+          <t>6.120</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -998,17 +998,17 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1024,85 +1024,109 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-25 23:30</t>
+          <t>2026-09-26 12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.280</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1113,7 +1137,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1123,52 +1147,52 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-22 10:45</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>1.641</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1176,17 +1200,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1202,85 +1226,109 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-26 14:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.410</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.060</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1291,12 +1339,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 13:00</t>
+          <t>2026-09-26 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1306,47 +1354,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.380</t>
+          <t>1.653</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>4.420</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>4.130</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1354,17 +1402,17 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>1.787</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.010</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1380,12 +1428,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 14:15</t>
+          <t>2026-09-26 16:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1395,70 +1443,94 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>4.750</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1469,85 +1541,109 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00</t>
+          <t>2026-09-26 16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1558,62 +1654,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-sport-recife/1637098349</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-26 19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.740</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1621,17 +1717,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1647,62 +1743,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-ceara/1637110355</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-26 19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1710,17 +1806,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1736,12 +1832,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-sport-recife/1637098349</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30</t>
+          <t>2026-09-26 21:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1751,47 +1847,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1799,17 +1895,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1825,47 +1921,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30</t>
+          <t>2026-09-27 12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.880</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1875,12 +1971,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.740</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1888,17 +1984,17 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1914,62 +2010,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00</t>
+          <t>2026-09-27 14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1982,12 +2078,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2028,22 +2124,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.920</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2053,12 +2149,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2092,7 +2188,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2107,32 +2203,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>4.230</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2142,12 +2238,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2155,17 +2251,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2181,7 +2277,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2196,32 +2292,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.130</t>
+          <t>4.140</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2231,12 +2327,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2244,17 +2340,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2295,22 +2391,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2320,12 +2416,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2333,17 +2429,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2359,12 +2455,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-27 21:30</t>
+          <t>2026-09-27 19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2374,47 +2470,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22 10:47</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.580</t>
+          <t>4.190</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2427,12 +2523,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2448,52 +2544,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-28 18:30</t>
+          <t>2026-09-27 21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22 10:46</t>
+          <t>2026-09-24 10:57</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>1.680</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>5.580</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2503,7 +2599,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2511,17 +2607,17 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2537,47 +2633,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30</t>
+          <t>2026-09-28 18:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22 10:47</t>
+          <t>2026-09-24 10:56</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>2.260</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2587,12 +2683,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2600,17 +2696,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2623,6 +2719,184 @@
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:57</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3.090</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.340</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.310</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:57</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.227</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5.670</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12.970</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-mikkelin-palloilijat/1636953757</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-fc-haka/1636953776</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:30</t>
+          <t>2026-09-25 16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,70 +570,94 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:59</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>6.060</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.360</t>
+          <t>4.880</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.890</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -644,85 +668,109 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-fc-haka/1636953776</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 16:00</t>
+          <t>2026-09-25 18:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.600</t>
+          <t>4.470</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>5.960</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -733,47 +781,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 18:30</t>
+          <t>2026-09-25 22:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:59</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>1.581</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>4.060</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.460</t>
+          <t>6.060</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,57 +831,57 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>1.943</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.909</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -846,12 +894,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 22:30</t>
+          <t>2026-09-25 23:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -861,70 +909,94 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 10:59</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.740</t>
+          <t>6.330</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -935,85 +1007,109 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25 23:30</t>
+          <t>2026-09-26 12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.120</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>1.787</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1024,7 +1120,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1034,72 +1130,72 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:59</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>1.641</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>4.500</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1109,22 +1205,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1137,12 +1233,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-26 13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1152,70 +1248,94 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:59</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.500</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1251,22 +1371,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1276,14 +1396,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>8.5</t>
@@ -1291,27 +1411,27 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1364,22 +1484,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 10:59</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.653</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.420</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.130</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1389,35 +1509,59 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1453,22 +1597,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.750</t>
+          <t>4.450</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1478,12 +1622,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1493,42 +1637,42 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1566,12 +1710,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.100</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1581,7 +1725,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1591,12 +1735,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1606,12 +1750,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1621,27 +1765,27 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>1.775</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.990</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1654,7 +1798,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-sport-recife/1637098349</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-ceara/1637110355</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1669,70 +1813,94 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1743,12 +1911,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-ceara/1637110355</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30</t>
+          <t>2026-09-26 21:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1758,42 +1926,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.020</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1801,27 +1969,51 @@
           <t>2.060</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1832,85 +2024,109 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30</t>
+          <t>2026-09-27 12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.010</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>1.793</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1921,67 +2137,79 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00</t>
+          <t>2026-09-27 14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -1989,17 +2217,29 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2010,62 +2250,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-27 14:00</t>
+          <t>2026-09-27 14:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2078,12 +2318,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2099,12 +2339,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15</t>
+          <t>2026-09-27 16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2114,32 +2354,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>4.140</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2149,17 +2389,29 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -2167,17 +2419,29 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2188,7 +2452,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2203,47 +2467,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3.340</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4.160</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3.270</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4.230</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2251,17 +2515,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2277,12 +2541,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-oviedo-vs-sporting-gijon/1637154833</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30</t>
+          <t>2026-09-27 19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2292,32 +2556,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2327,12 +2591,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2340,17 +2604,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2366,7 +2630,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-oviedo-vs-sporting-gijon/1637154833</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2376,37 +2640,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.980</t>
+          <t>4.190</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2416,17 +2680,29 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -2434,17 +2710,29 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>1.813</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2455,12 +2743,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00</t>
+          <t>2026-09-27 21:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2470,52 +2758,64 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.653</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.190</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -2523,17 +2823,29 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2544,85 +2856,109 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-27 21:30</t>
+          <t>2026-09-28 18:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 10:58</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.580</t>
+          <t>2.360</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2633,47 +2969,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-28 18:30</t>
+          <t>2026-09-28 22:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-24 10:56</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.260</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2683,35 +3019,59 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2722,12 +3082,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30</t>
+          <t>2026-09-29 22:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2737,47 +3097,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-24 10:57</t>
+          <t>2026-09-25 11:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>1.227</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>5.670</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>12.970</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2785,17 +3145,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2808,95 +3168,6 @@
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:57</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.227</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>5.670</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>12.970</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-fc-haka/1636953776</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 16:00</t>
+          <t>2026-09-26 12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-25 10:59</t>
+          <t>2026-09-26 10:38</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.060</t>
+          <t>3.020</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.880</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,47 +668,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/girona-vs-albacete/1636986794</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 18:30</t>
+          <t>2026-09-26 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.470</t>
+          <t>4.910</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.960</t>
+          <t>4.560</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -718,44 +718,44 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>-2.5</t>
@@ -763,12 +763,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-sao-bernardo/1637012425</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 22:30</t>
+          <t>2026-09-26 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-25 10:59</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.060</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.060</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,77 +894,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-londrina/1637020548</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 23:30</t>
+          <t>2026-09-26 14:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-25 10:59</t>
+          <t>2026-09-26 10:38</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.330</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,27 +974,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>1.819</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.900</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-26 16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.621</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>4.610</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>4.510</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,107 +1120,107 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-26 16:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Tenerife</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-25 10:59</t>
+          <t>2026-09-26 10:38</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.500</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>4.880</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,107 +1233,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 13:00</t>
+          <t>2026-09-26 16:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Celta Vigo II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-25 10:59</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,47 +1346,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-ceara/1637110355</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 14:15</t>
+          <t>2026-09-26 19:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-sport-recife/1637098349</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00</t>
+          <t>2026-09-26 19:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-25 10:59</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>1.775</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.943</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,62 +1572,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-26 21:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.450</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1637,42 +1637,42 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,12 +1685,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-27 12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1700,92 +1700,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,12 +1798,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-ceara/1637110355</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30</t>
+          <t>2026-09-27 14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1813,62 +1813,62 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>1.671</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>5.290</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1878,27 +1878,27 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,87 +1911,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30</t>
+          <t>2026-09-27 14:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.020</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00</t>
+          <t>2026-09-27 16:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2039,47 +2039,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2104,27 +2104,27 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,107 +2137,107 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-27 14:00</t>
+          <t>2026-09-27 16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>4.290</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2250,12 +2250,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-oviedo-vs-sporting-gijon/1637154833</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15</t>
+          <t>2026-09-27 19:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2265,32 +2265,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2300,35 +2300,59 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2339,47 +2363,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30</t>
+          <t>2026-09-27 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>4.190</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2389,57 +2413,57 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2452,85 +2476,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30</t>
+          <t>2026-09-27 21:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.653</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>5.780</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2541,37 +2589,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-oviedo-vs-sporting-gijon/1637154833</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00</t>
+          <t>2026-09-28 22:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-25 10:58</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2581,45 +2629,69 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2630,12 +2702,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00</t>
+          <t>2026-09-29 22:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2645,92 +2717,92 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00</t>
+          <t>2026-09-26 10:40</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.227</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>5.670</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.190</t>
+          <t>12.970</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.813</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2743,109 +2815,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-egersunds/1637171973</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-27 21:30</t>
+          <t>2026-10-02 17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00</t>
+          <t>2026-09-26 10:39</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.653</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.780</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2853,321 +2901,6 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-09-28 18:30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Spain - Segunda</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Castellon</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-25 10:58</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>3.120</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.260</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2.360</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-09-28 22:30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>America Mineiro</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-25 11:00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>3.430</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.170</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2.230</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-25 11:00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.227</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>5.670</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12.970</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/ceuta-vs-real-sociedad-ii/1637067778</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-27 12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,62 +570,62 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-26 10:38</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.020</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-sjk-akatemia/1637067792</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00</t>
+          <t>2026-09-27 14:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.910</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.560</t>
+          <t>5.930</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-pk-35/1637069498</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26 13:00</t>
+          <t>2026-09-27 14:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,12 +894,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/granada-vs-fc-andorra/1637080852</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:15</t>
+          <t>2026-09-27 16:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -909,32 +909,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Eldense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-26 10:38</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -944,27 +944,27 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,27 +974,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-japs/1637098261</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26 16:00</t>
+          <t>2026-09-27 16:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-26 10:40</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.610</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.510</t>
+          <t>4.870</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/tenerife-vs-cadiz/1637095198</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-oviedo-vs-sporting-gijon/1637154833</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-27 19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,92 +1135,92 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tenerife</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-26 10:38</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.170</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4.160</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.390</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4.880</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,52 +1233,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/celta-vigo-ii-vs-sabadell/1637095197</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30</t>
+          <t>2026-09-27 19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Celta Vigo II</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sabadell</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1288,52 +1288,52 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-ceara/1637110355</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30</t>
+          <t>2026-09-27 21:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1361,62 +1361,62 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-26 10:40</t>
+          <t>2026-09-27 11:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>1.581</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>6.380</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>1.961</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.925</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,77 +1459,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-sport-recife/1637098349</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/leganes-vs-castellon/1637159113</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 19:30</t>
+          <t>2026-09-28 18:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-26 10:40</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.050</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,12 +1572,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-atletico-goianiense/1637113350</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30</t>
+          <t>2026-09-28 22:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1587,92 +1587,92 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-26 10:40</t>
+          <t>2026-09-27 11:13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,107 +1685,107 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-valladolid-vs-cordoba/1637143719</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00</t>
+          <t>2026-09-29 22:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>1.227</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>5.670</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>12.970</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>1.793</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,109 +1798,85 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-avai/1637148516</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-egersunds/1637171973</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-27 14:00</t>
+          <t>2026-10-02 17:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-26 10:40</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.290</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1911,109 +1887,85 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/mallorca-vs-almeria/1637148534</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-sandnes-ulf/1637165570</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15</t>
+          <t>2026-10-03 12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.370</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -2024,109 +1976,85 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/eibar-vs-las-palmas/1637154808</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-asane/1637171509</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30</t>
+          <t>2026-10-03 14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.130</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>9.500</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>12.550</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2137,109 +2065,85 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/burgos-vs-eldense/1637154807</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-odd-bk/1637165569</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30</t>
+          <t>2026-10-03 14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eldense</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>3.760</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.230</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3.380</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.290</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2250,109 +2154,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/real-oviedo-vs-sporting-gijon/1637154833</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-stabaek/1637165568</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00</t>
+          <t>2026-10-03 14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain - Segunda</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-26 10:39</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>4.190</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
           <t>1.892</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2363,79 +2243,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-cuiaba/1637154834</t>
+          <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/sabadell-vs-fc-andorra/1637406700</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00</t>
+          <t>2026-10-03 16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Spain - Segunda</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sabadell</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-26 10:40</t>
+          <t>2026-09-27 11:12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.190</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -2443,29 +2311,17 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2473,434 +2329,6 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-athletic-club/1637155112</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-27 21:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-26 10:40</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1.653</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3.530</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5.780</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-juventude/1637175370</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-28 22:30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>America Mineiro</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-26 10:40</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>3.430</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3.170</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2.230</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-ponte-preta/1637209891</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-26 10:40</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1.227</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>5.670</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12.970</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-egersunds/1637171973</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-10-02 17:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Norway - 1st Division</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Ranheim</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Egersunds</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-26 10:39</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4.160</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3.040</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -552,6 +552,718 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wieczysta-krakow-vs-wisla-plock/1637178773</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Wieczysta Krakow</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Wisla Plock</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:54</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.160</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.600</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3.180</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/galatasaray-vs-kasimpasa/1637175572</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:55</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.234</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6.330</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10.640</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/moreirense-vs-gil-vicente/1637175573</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Moreirense</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:56</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3.600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.100</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.230</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GKS Katowice</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:55</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.170</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.950</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.920</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-pogon-siedlce/1637352530</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Podbeskidzie Bielsko-Biala</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pogon Siedlce</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:55</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.690</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4.250</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5.430</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6.850</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:57</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3.410</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.440</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2.140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Genclerbirligi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Amedspor</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:55</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.590</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.520</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.310</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.740</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-03 10:54</t>
+          <t>2026-10-04 11:37</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55</t>
+          <t>2026-10-04 11:37</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.234</t>
+          <t>1.238</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.330</t>
+          <t>6.260</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.640</t>
+          <t>10.520</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-03 10:56</t>
+          <t>2026-10-04 11:38</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55</t>
+          <t>2026-10-04 11:37</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55</t>
+          <t>2026-10-04 11:37</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1025,22 +1025,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55</t>
+          <t>2026-10-04 11:38</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.430</t>
+          <t>5.420</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.850</t>
+          <t>6.890</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-03 10:57</t>
+          <t>2026-10-04 11:38</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55</t>
+          <t>2026-10-04 11:37</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1264,6 +1264,1697 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cracovia Krakow</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zaglebie Lubin</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.430</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.180</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.460</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3.650</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Erzurumspor</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.120</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.700</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.751</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Polonia Warsaw</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.270</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3.480</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.960</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Unia Skierniewice</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nieciecza</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2.580</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.660</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2.470</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pogon Grodzisk Mazowiecki</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2.180</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3.460</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.130</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2.300</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.980</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2.840</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.436</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4.860</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7.010</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mainz 05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.960</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.960</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.230</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4.820</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4.680</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.606</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8.930</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8.680</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.215</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>+2.25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4.300</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.370</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Slask Wroclaw</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4.900</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4.480</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4.370</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.030</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.735</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.543</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4.990</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5.110</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-10 18:15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2.550</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.410</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.710</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-10 19:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Academico de Viseu</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2.290</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.380</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3.150</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Stal Mielec</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Warta Poznan</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:37</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2.920</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2.190</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Konyaspor</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:38</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2.570</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3.420</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2.720</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -733,62 +733,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/moreirense-vs-gil-vicente/1637175573</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 17:45</t>
+          <t>2026-10-09 18:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -796,17 +796,17 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -832,52 +832,52 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.403</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>6.970</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -885,17 +885,17 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -911,62 +911,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-pogon-siedlce/1637352530</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:30</t>
+          <t>2026-10-09 19:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Podbeskidzie Bielsko-Biala</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -979,12 +979,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1000,62 +1000,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09 18:30</t>
+          <t>2026-10-10 10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Amedspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>2.370</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.420</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.890</t>
+          <t>2.520</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1063,17 +1063,17 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1089,62 +1089,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09 19:15</t>
+          <t>2026-10-10 12:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 10:30</t>
+          <t>2026-10-10 13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1193,47 +1193,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Amedspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.740</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1267,47 +1267,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:45</t>
+          <t>2026-10-10 13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Erzurumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1330,17 +1330,17 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1356,62 +1356,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1419,17 +1419,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1445,62 +1445,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Erzurumspor</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1508,17 +1508,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1549,32 +1549,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1597,17 +1597,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1633,52 +1633,52 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>9.500</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>9.030</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>1.208</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1686,17 +1686,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,52 +1722,52 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>4.840</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>4.710</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1775,17 +1775,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1816,47 +1816,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.980</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.840</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1864,7 +1864,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1915,22 +1915,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.860</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.010</t>
+          <t>7.090</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -1979,7 +1979,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1994,47 +1994,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2042,17 +2042,17 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2068,62 +2068,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.820</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.680</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.606</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>1.917</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.970</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2131,17 +2131,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2157,52 +2157,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.930</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.680</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2220,17 +2220,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2246,62 +2246,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-10 14:30</t>
+          <t>2026-10-10 16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>4.370</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>4.030</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.917</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2309,17 +2309,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2335,62 +2335,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30</t>
+          <t>2026-10-10 16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>4.990</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>5.150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2424,62 +2424,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00</t>
+          <t>2026-10-10 18:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.030</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2513,62 +2513,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.990</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.110</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2576,12 +2576,12 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2602,62 +2602,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-11 10:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2665,17 +2665,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2691,62 +2691,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-11 10:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>2.620</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2780,12 +2780,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00</t>
+          <t>2026-10-11 12:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2795,47 +2795,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-04 11:37</t>
+          <t>2026-10-05 13:14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2843,17 +2843,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2869,47 +2869,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 10:30</t>
+          <t>2026-10-11 12:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istanbul Basaksehir</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-04 11:38</t>
+          <t>2026-10-05 13:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2955,6 +2955,896 @@
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-11 13:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Corum Belediyespor</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2.700</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.340</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2.630</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-11 13:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Borussia Monchengladbach</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4.150</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3.260</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rio Ave</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Nacional da Madeira</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2.340</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3.190</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Puszcza Niepolomice</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Polonia Bytom</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.470</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3.720</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2.550</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Korona Kielce</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.290</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.080</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3.390</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Germany - Bundesliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.666</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.930</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5.280</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.261</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>5.800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10.270</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-11 18:15</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Legia Warsaw</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Wisla Krakow</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:13</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3.840</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3.410</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-11 18:15</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Odra Opole</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Miedz Legnica</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:14</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.440</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.420</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2.750</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-11 19:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Estrela da Amadora</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:16</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2.170</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3.530</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1.251</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.260</t>
+          <t>6.020</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.520</t>
+          <t>10.280</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -733,62 +733,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/moreirense-vs-gil-vicente/1637175573</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 18:30</t>
+          <t>2026-10-09 17:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -796,17 +796,17 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -832,52 +832,52 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.970</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -885,17 +885,17 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -911,75 +911,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 19:15</t>
+          <t>2026-10-09 18:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-05 13:15</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>5.500</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>7.070</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -987,9 +999,21 @@
           <t>1.847</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1000,62 +1024,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-10 10:30</t>
+          <t>2026-10-09 19:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Amedspor</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.370</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1063,17 +1087,17 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1089,62 +1113,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:45</t>
+          <t>2026-10-10 10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Amedspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1152,17 +1176,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1178,62 +1202,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-10 12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1241,17 +1265,17 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1267,7 +1291,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1282,47 +1306,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Erzurumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1330,17 +1354,17 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1381,7 +1405,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1445,7 +1469,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1460,32 +1484,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1495,12 +1519,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1508,17 +1532,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1534,7 +1558,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1544,75 +1568,99 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>1.440</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>4.910</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>7.120</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1623,7 +1671,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1638,70 +1686,94 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.500</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9.030</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.208</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1712,7 +1784,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1727,70 +1799,94 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.840</t>
+          <t>9.550</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.710</t>
+          <t>9.070</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.207</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1801,7 +1897,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1816,47 +1912,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>3.920</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1864,7 +1960,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1890,7 +1986,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1905,47 +2001,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>5.020</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>4.760</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.090</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1958,12 +2054,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -1979,62 +2075,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2042,17 +2138,17 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2068,62 +2164,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-10 14:30</t>
+          <t>2026-10-10 15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-05 13:15</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2131,17 +2227,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2157,62 +2253,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30</t>
+          <t>2026-10-10 16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>4.430</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2220,17 +2316,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2246,85 +2342,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00</t>
+          <t>2026-10-10 16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.030</t>
+          <t>4.940</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>4.980</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2335,62 +2455,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-10 18:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.990</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.150</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2398,17 +2518,17 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2424,62 +2544,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2487,7 +2607,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2497,7 +2617,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2513,62 +2633,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-11 10:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-05 13:15</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2576,17 +2696,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2602,62 +2722,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00</t>
+          <t>2026-10-11 10:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>2.730</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2665,17 +2785,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2691,47 +2811,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-11 10:30</t>
+          <t>2026-10-11 12:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istanbul Basaksehir</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.620</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2741,12 +2861,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2754,17 +2874,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2780,47 +2900,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:30</t>
+          <t>2026-10-11 12:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2830,12 +2950,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2848,12 +2968,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2869,47 +2989,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 12:45</t>
+          <t>2026-10-11 13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.700</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>2.630</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2919,12 +3039,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2932,17 +3052,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2958,85 +3078,109 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-11 13:00</t>
+          <t>2026-10-11 13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.700</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3047,62 +3191,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 13:30</t>
+          <t>2026-10-11 14:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>Nacional da Madeira</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:35</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3110,17 +3254,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3136,62 +3280,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30</t>
+          <t>2026-10-11 15:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nacional da Madeira</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-05 13:15</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3199,17 +3343,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3225,62 +3369,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3293,12 +3437,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3314,7 +3458,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,52 +3468,52 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>1.684</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>5.230</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3377,17 +3521,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3403,62 +3547,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-11 16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:34</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>5.720</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.280</t>
+          <t>10.200</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3476,7 +3620,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3492,62 +3636,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10.270</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3560,12 +3704,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3581,7 +3725,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3591,52 +3735,52 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-05 13:13</t>
+          <t>2026-10-06 12:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>2.750</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3644,17 +3788,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3670,62 +3814,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-11 19:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Estrela da Amadora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-05 13:14</t>
+          <t>2026-10-06 12:35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -3733,17 +3877,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -3759,62 +3903,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estrela da Amadora</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-05 13:16</t>
+          <t>2026-10-06 12:32</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -3822,17 +3966,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3845,6 +3989,273 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Stal Rzeszow</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:33</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.910</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.850</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2.160</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Eyupspor</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:34</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3.620</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.570</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:15</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Famalicao</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:35</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.290</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4.920</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,17 +580,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.160</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -623,12 +623,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -669,22 +669,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1.244</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.020</t>
+          <t>6.140</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.280</t>
+          <t>10.390</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-06 12:35</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-pogon-siedlce/1637352530</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -832,52 +832,52 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Podbeskidzie Bielsko-Biala</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -885,17 +885,17 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -936,22 +936,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.500</t>
+          <t>5.720</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.070</t>
+          <t>7.510</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06 12:35</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erzurumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1354,17 +1354,17 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1380,62 +1380,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1443,17 +1443,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,47 +1484,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1532,17 +1532,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,99 +1568,75 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.440</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.910</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.120</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1671,7 +1647,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1681,99 +1657,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1809,22 +1761,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.550</t>
+          <t>10.090</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9.070</t>
+          <t>9.330</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.207</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1834,57 +1786,57 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -1897,7 +1849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1912,70 +1864,94 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>1.440</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>4.910</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>7.130</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -1986,7 +1962,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2001,70 +1977,94 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.020</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.760</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2075,62 +2075,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-10 14:30</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-06 12:35</t>
+          <t>2026-10-07 12:29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>4.970</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>4.800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1.917</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2138,17 +2138,17 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2164,62 +2164,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30</t>
+          <t>2026-10-10 14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2227,17 +2227,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2253,62 +2253,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00</t>
+          <t>2026-10-10 15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.430</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2316,17 +2316,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2342,109 +2342,85 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-10 16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.940</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.980</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2455,85 +2431,109 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-10 16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>4.950</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>4.980</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2544,62 +2544,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-10 18:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-06 12:35</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2607,7 +2607,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2633,62 +2633,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2696,17 +2696,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2747,22 +2747,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.730</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2989,85 +2989,109 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 13:00</t>
+          <t>2026-10-11 13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.700</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3078,109 +3102,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-11 13:30</t>
+          <t>2026-10-11 14:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>Nacional da Madeira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>2.010</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3191,62 +3191,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30</t>
+          <t>2026-10-11 15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nacional da Madeira</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-06 12:35</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3254,17 +3254,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3280,62 +3280,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>5.340</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3343,17 +3343,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3369,62 +3369,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-11 16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>1.276</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>5.620</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>9.850</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3458,62 +3458,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5.230</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3547,62 +3547,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-06 12:34</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5.720</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10.200</t>
+          <t>2.750</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3610,17 +3610,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3636,62 +3636,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-11 19:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Estrela da Amadora</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3699,17 +3699,17 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3725,47 +3725,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3788,17 +3788,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3814,62 +3814,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Estrela da Amadora</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-06 12:35</t>
+          <t>2026-10-07 12:27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>2.160</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -3877,17 +3877,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -3903,62 +3903,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00</t>
+          <t>2026-10-12 17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-06 12:32</t>
+          <t>2026-10-07 12:28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>1.826</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2.020</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -3966,17 +3966,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3992,62 +3992,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00</t>
+          <t>2026-10-12 19:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Stal Rzeszow</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-06 12:33</t>
+          <t>2026-10-07 12:30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.160</t>
+          <t>4.920</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4055,17 +4055,17 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -4078,184 +4078,6 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-10-12 17:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Turkey - Super Lig</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Eyupspor</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Goztepe</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-06 12:34</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>3.620</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3.570</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:15</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Portugal - Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Famalicao</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-06 12:35</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3.290</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4.920</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07 12:25</t>
+          <t>2026-10-08 12:34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -623,12 +623,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -669,22 +669,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1.251</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.140</t>
+          <t>6.090</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.390</t>
+          <t>10.050</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -758,22 +758,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -801,12 +801,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-pogon-siedlce/1637352530</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -832,52 +832,52 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Podbeskidzie Bielsko-Biala</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:34</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -885,17 +885,17 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -936,22 +936,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.720</t>
+          <t>5.770</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.510</t>
+          <t>7.760</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -961,52 +961,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>2.040</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1049,37 +1049,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1227,22 +1227,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Erzurumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1354,17 +1354,17 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1395,47 +1395,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Erzurumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1443,17 +1443,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,47 +1484,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1532,17 +1532,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,47 +1573,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1621,17 +1621,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1710,17 +1710,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1751,92 +1751,92 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10.090</t>
+          <t>4.940</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9.330</t>
+          <t>4.770</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -1874,22 +1874,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.440</t>
+          <t>1.458</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.910</t>
+          <t>4.860</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.130</t>
+          <t>6.830</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1899,42 +1899,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1977,92 +1977,92 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07 12:29</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>2.370</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.840</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2090,37 +2090,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-07 12:29</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.970</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.800</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2133,27 +2133,51 @@
           <t>1.934</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2164,85 +2188,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-10 14:30</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>10.460</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>9.430</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>1.189</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>+2.25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2253,62 +2301,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30</t>
+          <t>2026-10-10 14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>4.620</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2316,17 +2364,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2342,62 +2390,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00</t>
+          <t>2026-10-10 15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>4.920</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>4.450</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>1.961</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.892</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2405,17 +2453,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2431,109 +2479,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-10 16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-07 12:29</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.950</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.980</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2544,70 +2568,82 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-10 16:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>5.010</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2617,12 +2653,24 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2633,12 +2681,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/maritimo-vs-porto/1637178760</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-10 17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2648,47 +2696,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:37</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>8.730</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>5.070</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>1.341</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2696,17 +2744,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2722,47 +2770,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-11 10:30</t>
+          <t>2026-10-10 18:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Istanbul Basaksehir</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2772,12 +2820,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2790,12 +2838,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2811,62 +2859,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:30</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2874,17 +2922,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2900,62 +2948,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:45</t>
+          <t>2026-10-11 10:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2963,17 +3011,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2989,109 +3037,85 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 13:30</t>
+          <t>2026-10-11 10:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-07 12:29</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3102,62 +3126,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30</t>
+          <t>2026-10-11 12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nacional da Madeira</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3165,17 +3189,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3191,47 +3215,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00</t>
+          <t>2026-10-11 12:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3241,12 +3265,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3254,17 +3278,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3280,62 +3304,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-11 13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-07 12:29</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5.340</t>
+          <t>2.640</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3343,17 +3367,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3369,85 +3393,109 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00</t>
+          <t>2026-10-11 13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5.620</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9.850</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -3458,57 +3506,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-11 14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Nacional da Madeira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:37</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3521,17 +3569,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3547,12 +3595,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-11 15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3562,32 +3610,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3597,12 +3645,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3615,12 +3663,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3636,47 +3684,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estrela da Amadora</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3686,12 +3734,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3699,17 +3747,17 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3725,62 +3773,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-07 12:26</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>1.684</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>5.360</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3793,12 +3841,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3814,62 +3862,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00</t>
+          <t>2026-10-11 16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Stal Rzeszow</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-07 12:27</t>
+          <t>2026-10-08 12:36</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>5.410</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.160</t>
+          <t>9.900</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -3877,17 +3925,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -3903,62 +3951,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00</t>
+          <t>2026-10-11 17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Eyupspor</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-07 12:28</t>
+          <t>2026-10-08 12:37</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.620</t>
+          <t>1.216</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>6.690</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>10.990</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -3966,17 +4014,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3992,47 +4040,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-12 19:15</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-07 12:30</t>
+          <t>2026-10-08 12:35</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.920</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4042,12 +4090,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4055,17 +4103,17 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -4078,6 +4126,451 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-11 18:15</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Odra Opole</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Miedz Legnica</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:35</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.430</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.400</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.780</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-11 19:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Portugal - Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Estrela da Amadora</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:37</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.530</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3.480</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Poland - Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Motor Lublin</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:35</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.580</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.170</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2.850</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Poland - 1st Liga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Stal Rzeszow</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:35</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2.950</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3.790</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2.150</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Turkey - Super Lig</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Eyupspor</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:36</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3.920</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,17 +580,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-08 12:34</t>
+          <t>2026-10-09 12:22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -605,17 +605,29 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -623,17 +635,29 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -669,22 +693,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1.278</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.090</t>
+          <t>6.080</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.050</t>
+          <t>10.210</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -694,17 +718,29 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>3.25</t>
@@ -712,17 +748,29 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -758,22 +806,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,35 +831,59 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -847,12 +919,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-08 12:34</t>
+          <t>2026-10-09 12:22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -862,7 +934,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -872,35 +944,59 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -911,7 +1007,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-pogon-siedlce/1637352530</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -921,97 +1017,97 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Podbeskidzie Bielsko-Biala</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Pogon Siedlce</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.770</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.760</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>-1.5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1.869</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.813</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1024,85 +1120,109 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09 19:15</t>
+          <t>2026-10-09 18:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>5.640</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>7.890</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1113,85 +1233,109 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-10 10:30</t>
+          <t>2026-10-09 19:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Amedspor</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1202,62 +1346,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:45</t>
+          <t>2026-10-10 10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Amedspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1265,17 +1409,17 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1291,85 +1435,109 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-10 12:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1405,22 +1573,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1430,12 +1598,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1448,12 +1616,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1469,85 +1637,109 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1558,7 +1750,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,70 +1765,94 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1647,7 +1863,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1662,47 +1878,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1710,17 +1926,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1736,7 +1952,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1746,99 +1962,75 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.940</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.770</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1874,22 +2066,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1.446</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.860</t>
+          <t>4.920</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.830</t>
+          <t>6.960</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1899,24 +2091,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>1.892</t>
@@ -1924,32 +2116,32 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>1.847</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -1987,22 +2179,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.370</t>
+          <t>2.400</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.840</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2012,44 +2204,44 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>-0.5</t>
@@ -2057,7 +2249,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2100,22 +2292,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2213,22 +2405,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.460</t>
+          <t>10.490</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9.430</t>
+          <t>9.330</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.189</t>
+          <t>1.190</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2238,12 +2430,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2253,29 +2445,29 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>+3.5</t>
@@ -2283,12 +2475,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2326,22 +2518,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.620</t>
+          <t>4.570</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2351,17 +2543,29 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -2374,12 +2578,24 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2415,7 +2631,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2440,12 +2656,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2458,12 +2674,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2479,85 +2695,109 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00</t>
+          <t>2026-10-10 16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>4.960</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>4.810</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2568,109 +2808,85 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/maritimo-vs-porto/1637178760</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-10 17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>9.350</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.010</t>
+          <t>5.150</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2681,67 +2897,79 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/maritimo-vs-porto/1637178760</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00</t>
+          <t>2026-10-10 18:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-08 12:37</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.730</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5.070</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.341</t>
+          <t>2.720</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -2749,17 +2977,29 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2770,62 +3010,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2833,17 +3073,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2859,62 +3099,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-11 10:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-08 12:37</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2922,17 +3162,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2948,32 +3188,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00</t>
+          <t>2026-10-11 10:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2983,50 +3223,74 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3037,47 +3301,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 10:30</t>
+          <t>2026-10-11 12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istanbul Basaksehir</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3087,17 +3351,29 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3105,17 +3381,29 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3126,47 +3414,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-11 12:30</t>
+          <t>2026-10-11 12:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3176,17 +3464,29 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3194,17 +3494,29 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3215,47 +3527,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 12:45</t>
+          <t>2026-10-11 13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.620</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3265,12 +3577,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3278,17 +3590,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3304,85 +3616,109 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-11 13:00</t>
+          <t>2026-10-11 13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>3.220</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3393,47 +3729,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-11 13:30</t>
+          <t>2026-10-11 14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>Nacional da Madeira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3443,17 +3779,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3463,12 +3799,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3478,22 +3814,22 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -3506,85 +3842,109 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30</t>
+          <t>2026-10-11 15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nacional da Madeira</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-08 12:37</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -3595,85 +3955,109 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -3684,7 +4068,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3694,57 +4078,69 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>5.850</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3752,17 +4148,29 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -3773,85 +4181,109 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-11 16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>5.410</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.360</t>
+          <t>9.900</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>2.020</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -3862,85 +4294,109 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00</t>
+          <t>2026-10-11 17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.204</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.410</t>
+          <t>6.900</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.900</t>
+          <t>11.610</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -3951,62 +4407,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-11 17:00</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-08 12:37</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6.690</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10.990</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4014,17 +4470,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4040,7 +4496,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4050,75 +4506,99 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
@@ -4129,67 +4609,79 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-11 19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Estrela da Amadora</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -4197,17 +4689,29 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -4218,85 +4722,109 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estrela da Amadora</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-08 12:37</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -4307,7 +4835,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4317,52 +4845,52 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>2.950</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>2.150</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -4375,12 +4903,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4396,85 +4924,109 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00</t>
+          <t>2026-10-12 17:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Stal Rzeszow</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-08 12:35</t>
+          <t>2026-10-09 12:24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.950</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -4485,85 +5037,109 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00</t>
+          <t>2026-10-12 19:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Eyupspor</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-08 12:36</t>
+          <t>2026-10-09 12:25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>4.590</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/wieczysta-krakow-vs-wisla-plock/1637178773</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00</t>
+          <t>2026-10-10 12:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,92 +570,92 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Cracovia Krakow</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-09 12:22</t>
+          <t>2026-10-10 11:41</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>4.290</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,12 +668,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/galatasaray-vs-kasimpasa/1637175572</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09 17:00</t>
+          <t>2026-10-10 13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,92 +683,92 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>Erzurumspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.080</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.210</t>
+          <t>4.560</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/moreirense-vs-gil-vicente/1637175573</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 17:45</t>
+          <t>2026-10-10 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,107 +894,107 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/rakow-czestochowa-vs-gks-katowice/1637178774</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09 18:30</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-09 12:22</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>2.620</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.980</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/podbeskidzie-bielsko-biala-vs-pogon-siedlce/1637352530</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:30</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,92 +1022,92 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Podbeskidzie Bielsko-Biala</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pogon Siedlce</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>2.210</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.520</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.190</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.780</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3.990</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,107 +1120,107 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/borussia-dortmund-vs-werder-bremen/1636598006</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09 18:30</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.640</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.890</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,102 +1233,102 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/braga-vs-sporting-cp/1637181731</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09 19:15</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>12.310</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>8.560</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1346,42 +1346,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/genclerbirligi-vs-amedspor/1637178745</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 10:30</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Amedspor</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1396,35 +1396,59 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1435,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:45</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-09 12:22</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.420</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>5.310</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>7.150</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1548,85 +1572,109 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Erzurumspor</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>4.850</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>4.870</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1637,107 +1685,107 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-10 13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>2.860</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>1.970</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.917</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1750,87 +1798,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 15:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Slask Wroclaw</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>5.050</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>4.530</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1840,17 +1888,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1863,67 +1911,79 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>4.530</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>4.430</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>3</t>
@@ -1931,17 +1991,29 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1952,85 +2024,109 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 16:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>4.840</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2041,107 +2137,107 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/maritimo-vs-porto/1637178760</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.446</t>
+          <t>10.960</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.920</t>
+          <t>5.760</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.960</t>
+          <t>1.293</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>1.925</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.847</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2154,107 +2250,107 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 18:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Jagiellonia Bialystok</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.400</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2267,107 +2363,107 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2380,97 +2476,97 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-10 19:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.490</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9.330</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.190</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2480,7 +2576,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2493,109 +2589,85 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-10 14:30</t>
+          <t>2026-10-11 10:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.570</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.360</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2606,85 +2678,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30</t>
+          <t>2026-10-11 10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-09 12:22</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.920</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.450</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2695,107 +2791,107 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-11 12:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.960</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.810</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>1.900</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.806</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2808,85 +2904,109 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/maritimo-vs-porto/1637178760</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00</t>
+          <t>2026-10-11 12:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9.350</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.150</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2897,47 +3017,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-11 13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.560</t>
+          <t>2.620</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>2.730</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2947,59 +3067,35 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -3010,47 +3106,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-11 13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3060,35 +3156,59 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -3099,85 +3219,109 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00</t>
+          <t>2026-10-11 14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Nacional da Madeira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3188,47 +3332,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11 10:30</t>
+          <t>2026-10-11 15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istanbul Basaksehir</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3238,22 +3382,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3263,32 +3407,32 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -3301,77 +3445,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 12:30</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3381,27 +3525,27 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1.900</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -3414,107 +3558,107 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-11 12:45</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>1.649</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.940</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>5.640</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3527,12 +3671,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 13:00</t>
+          <t>2026-10-11 16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3542,70 +3686,94 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.620</t>
+          <t>1.284</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>5.440</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>9.960</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3616,77 +3784,77 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-11 13:30</t>
+          <t>2026-10-11 17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.189</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>7.180</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.220</t>
+          <t>12.360</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3696,27 +3864,27 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
@@ -3729,109 +3897,85 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nacional da Madeira</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -3842,12 +3986,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3857,32 +4001,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3892,47 +4036,47 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3955,47 +4099,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-11 19:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Estrela da Amadora</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4005,57 +4149,57 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4068,107 +4212,107 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.980</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5.850</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -4181,109 +4325,85 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-09 12:24</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>2.950</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5.410</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.900</t>
+          <t>2.150</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -4294,107 +4414,107 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-11 17:00</t>
+          <t>2026-10-12 17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6.900</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11.610</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4407,12 +4527,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-wieczysta-krakow/1637446213</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-12 18:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4422,47 +4542,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Legia Warsaw</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:42</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4470,17 +4590,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4496,102 +4616,102 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15</t>
+          <t>2026-10-12 19:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-09 12:23</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>4.590</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>2.040</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4609,109 +4729,85 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/eintracht-frankfurt-vs-fc-koln/1637151320</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30</t>
+          <t>2026-10-16 18:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Estrela da Amadora</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-09 12:25</t>
+          <t>2026-10-10 11:43</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -4719,434 +4815,6 @@
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-10-12 16:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Poland - Ekstraklasa</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Radomiak Radom</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Motor Lublin</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-09 12:23</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2.570</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3.170</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2.860</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-10-12 16:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Poland - 1st Liga</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Stal Rzeszow</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Lechia Gdansk</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-09 12:23</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2.950</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2.150</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-10-12 17:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Turkey - Super Lig</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Eyupspor</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Goztepe</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-09 12:24</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>3.910</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>3.760</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:15</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Portugal - Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Famalicao</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-09 12:25</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>3.300</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4.590</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/cracovia-krakow-vs-zaglebie-lubin/1637178775</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:45</t>
+          <t>2026-10-11 12:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Ruch Chorzow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10 11:41</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2.510</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.320</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.860</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3.470</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4.290</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/alanyaspor-vs-erzurumspor/1637178748</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-11 12:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Erzurumspor</t>
+          <t>Widzew Lodz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:54</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>2.810</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.420</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.560</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.280</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4.560</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2.010</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,12 +781,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/samsunspor-vs-trabzonspor/1637178747</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10 13:00</t>
+          <t>2026-10-11 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -796,92 +796,92 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.950</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,77 +894,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/unia-skierniewice-vs-nieciecza/1637396143</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.620</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,27 +974,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,47 +1007,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/chrobry-glogow-vs-pogon-grodzisk-mazowiecki/1637397488</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 14:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pogon Grodzisk Mazowiecki</t>
+          <t>Nacional da Madeira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:57</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1057,32 +1057,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/arka-gdynia-vs-polonia-warsaw/1637398417</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,82 +1135,82 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polonia Warsaw</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>2.590</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.670</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,107 +1233,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/augsburg-vs-bayern-munich/1636592218</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:54</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.310</t>
+          <t>2.370</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.560</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>2.020</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/mainz-05-vs-bayer-leverkusen/1636598004</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 15:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1361,92 +1361,92 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>1.699</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>5.100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hoffenheim-vs-hamburger-sv/1636590116</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.420</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.310</t>
+          <t>6.570</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.150</t>
+          <t>12.250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,62 +1572,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/paderborn-vs-stuttgart/1636592221</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 17:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:57</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.850</t>
+          <t>1.226</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.870</t>
+          <t>6.750</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>12.540</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1637,42 +1637,42 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,52 +1685,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-elversberg/1636598008</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10 13:30</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Legia Warsaw</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:54</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1750,42 +1750,42 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,72 +1798,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/slask-wroclaw-vs-lech-poznan/1637360367</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-10 15:30</t>
+          <t>2026-10-11 18:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.050</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.530</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1873,22 +1873,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1911,107 +1911,107 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/caykur-rizespor-vs-fenerbahce/1637178749</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00</t>
+          <t>2026-10-11 19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Portugal - Primeira Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Estrela da Amadora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:57</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.530</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.430</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,107 +2024,107 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/rb-leipzig-vs-eintracht-frankfurt/1636592222</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:54</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.840</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,109 +2137,85 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/maritimo-vs-porto/1637178760</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00</t>
+          <t>2026-10-12 16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Stal Rzeszow</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-10 11:43</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.960</t>
+          <t>2.610</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.760</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.293</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2250,107 +2226,107 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/jagiellonia-bialystok-vs-gornik-zabrze/1637183910</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-10 18:15</t>
+          <t>2026-10-12 17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystok</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>1.952</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1.847</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2363,47 +2339,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/academico-de-viseu-vs-estoril/1637175575</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/gks-katowice-vs-wieczysta-krakow/1637446213</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-12 18:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Poland - Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-10 11:43</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2413,59 +2389,35 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2476,12 +2428,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/casa-pia-vs-santa-clara/1637175574</t>
+          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/famalicao-vs-alverca/1637175577</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-10 19:30</t>
+          <t>2026-10-12 19:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2491,47 +2443,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-10 11:43</t>
+          <t>2026-10-11 11:57</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>4.590</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2541,42 +2493,42 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2589,12 +2541,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-mielec-vs-warta-poznan/1637426540</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/warta-poznan-vs-unia-skierniewice/1637973672</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00</t>
+          <t>2026-10-16 16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2604,47 +2556,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Warta Poznan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Warta Poznan</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2657,7 +2609,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2678,109 +2630,85 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/konyaspor-vs-istanbul-basaksehir/1637181716</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/eintracht-frankfurt-vs-fc-koln/1637151320</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-11 10:30</t>
+          <t>2026-10-16 18:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Istanbul Basaksehir</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.560</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2791,79 +2719,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/lks-lodz-vs-ruch-chorzow/1637429081</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/amedspor-vs-konyaspor/1638087093</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:30</t>
+          <t>2026-10-17 13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Amedspor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ruch Chorzow</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -2871,29 +2787,17 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2904,109 +2808,85 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/piast-gliwice-vs-widzew-lodz/1637181739</t>
+          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/pogon-grodzisk-mazowiecki-vs-polonia-warsaw/1638087096</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:45</t>
+          <t>2026-10-17 13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Poland - 1st Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Pogon Grodzisk Mazowiecki</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Widzew Lodz</t>
+          <t>Polonia Warsaw</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -3017,62 +2897,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/gaziantep-vs-corum-belediyespor/1637175580</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/werder-bremen-vs-paderborn/1637151319</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-11 13:00</t>
+          <t>2026-10-17 13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey - Super Lig</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.620</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.730</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -3080,17 +2960,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -3106,12 +2986,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/fc-koln-vs-borussia-monchengladbach/1636598005</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/hamburger-sv-vs-stuttgart/1637151323</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-11 13:30</t>
+          <t>2026-10-17 13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3121,94 +3001,70 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-10 11:43</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -3219,109 +3075,85 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/rio-ave-vs-nacional-da-madeira/1637175576</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/schalke-04-vs-mainz-05/1637148527</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30</t>
+          <t>2026-10-17 13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal - Primeira Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nacional da Madeira</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-10 11:43</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3332,47 +3164,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/puszcza-niepolomice-vs-polonia-bytom/1637432116</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/elversberg-vs-augsburg/1637146539</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00</t>
+          <t>2026-10-17 13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland - 1st Liga</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3382,59 +3214,35 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3445,109 +3253,85 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/pogon-szczecin-vs-korona-kielce/1637178776</t>
+          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/union-berlin-vs-borussia-dortmund/1637151318</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-17 13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland - Ekstraklasa</t>
+          <t>Germany - Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:57</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>4.630</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>1.649</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3558,109 +3342,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/freiburg-vs-schalke-04/1636590120</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/fenerbahce-vs-alanyaspor/1638089895</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30</t>
+          <t>2026-10-17 16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany - Bundesliga</t>
+          <t>Turkey - Super Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-10 11:43</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.341</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>5.250</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5.640</t>
+          <t>8.250</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3671,12 +3431,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/besiktas-vs-kocaelispor/1637181718</t>
+          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/kasimpasa-vs-samsunspor/1638184884</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00</t>
+          <t>2026-10-18 10:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3686,94 +3446,70 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-10 11:42</t>
+          <t>2026-10-11 11:56</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5.440</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9.960</t>
+          <t>2.670</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3781,1040 +3517,6 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/benfica-vs-vitoria-guimaraes/1637178761</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-11 17:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Portugal - Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Benfica</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Vitoria Guimaraes</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:43</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1.189</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>7.180</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12.360</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/legia-warsaw-vs-wisla-krakow/1637183911</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-10-11 18:15</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Poland - Ekstraklasa</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Legia Warsaw</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Wisla Krakow</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:42</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3.410</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/odra-opole-vs-miedz-legnica/1637436570</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-10-11 18:15</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Poland - 1st Liga</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Odra Opole</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Miedz Legnica</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:42</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2.430</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3.400</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2.780</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/arouca-vs-estrela-da-amadora/1637181732</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-10-11 19:30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Portugal - Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Arouca</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Estrela da Amadora</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:43</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3.460</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3.590</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/radomiak-radom-vs-motor-lublin/1637443897</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-10-12 16:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Poland - Ekstraklasa</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Radomiak Radom</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Motor Lublin</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:42</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2.450</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3.200</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3.000</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/stal-rzeszow-vs-lechia-gdansk/1637686818</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-10-12 16:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Poland - 1st Liga</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Stal Rzeszow</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Lechia Gdansk</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:42</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2.950</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2.150</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/turkey-super-league/eyupspor-vs-goztepe/1637181717</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-10-12 17:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Turkey - Super Lig</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Eyupspor</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Goztepe</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-10 11:42</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3.910</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.760</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="in